--- a/Dowling/dowling-vs-waterloo-west-092526.xlsx
+++ b/Dowling/dowling-vs-waterloo-west-092526.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R5216d5b5eef34bbc"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R526acbb4b78e47dd"/>
   </sheets>
 </workbook>
 </file>
@@ -112,6 +112,9 @@
     <t>A</t>
   </si>
   <si>
+    <t>R</t>
+  </si>
+  <si>
     <t>Pass</t>
   </si>
   <si>
@@ -149,9 +152,6 @@
   </si>
   <si>
     <t>MIRROR STORM</t>
-  </si>
-  <si>
-    <t>R</t>
   </si>
   <si>
     <t>IOWA</t>
@@ -432,6 +432,9 @@
       <c r="M3" t="s">
         <v>32</v>
       </c>
+      <c r="U3" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4">
@@ -456,10 +459,10 @@
         <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -472,6 +475,9 @@
       </c>
       <c r="O4">
         <v>1</v>
+      </c>
+      <c r="U4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -494,7 +500,7 @@
         <v>-31</v>
       </c>
       <c r="G5" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H5" t="s">
         <v>30</v>
@@ -509,6 +515,9 @@
         <v>6</v>
       </c>
       <c r="M5" t="s">
+        <v>37</v>
+      </c>
+      <c r="U5" t="s">
         <v>36</v>
       </c>
     </row>
@@ -532,13 +541,13 @@
         <v>-32</v>
       </c>
       <c r="G6" t="s">
+        <v>36</v>
+      </c>
+      <c r="H6" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" t="s">
         <v>35</v>
-      </c>
-      <c r="H6" t="s">
-        <v>33</v>
-      </c>
-      <c r="I6" t="s">
-        <v>34</v>
       </c>
       <c r="J6">
         <v>22</v>
@@ -552,6 +561,9 @@
       <c r="O6">
         <v>4</v>
       </c>
+      <c r="U6" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7">
@@ -573,7 +585,7 @@
         <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
         <v>30</v>
@@ -589,6 +601,9 @@
       </c>
       <c r="M7" t="s">
         <v>32</v>
+      </c>
+      <c r="U7" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="8">
@@ -628,6 +643,9 @@
       <c r="M8" t="s">
         <v>32</v>
       </c>
+      <c r="U8" t="s">
+        <v>33</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9">
@@ -652,10 +670,10 @@
         <v>26</v>
       </c>
       <c r="H9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I9" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -668,6 +686,9 @@
       </c>
       <c r="O9">
         <v>4</v>
+      </c>
+      <c r="U9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -693,10 +714,10 @@
         <v>26</v>
       </c>
       <c r="H10" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I10" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="Q10">
         <v>15</v>
@@ -710,7 +731,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -722,19 +743,19 @@
         <v>-29</v>
       </c>
       <c r="G11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L11">
         <v>7</v>
@@ -746,10 +767,13 @@
         <v>9</v>
       </c>
       <c r="S11" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T11" t="s">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="U11" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="12">
@@ -760,7 +784,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -772,7 +796,7 @@
         <v>-29</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H12" t="s">
         <v>30</v>
@@ -784,7 +808,7 @@
         <v>8</v>
       </c>
       <c r="K12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L12">
         <v>7</v>
@@ -793,10 +817,13 @@
         <v>29</v>
       </c>
       <c r="S12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T12" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="U12" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="13">
@@ -807,7 +834,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -819,7 +846,7 @@
         <v>-37</v>
       </c>
       <c r="G13" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H13" t="s">
         <v>30</v>
@@ -831,7 +858,7 @@
         <v>7</v>
       </c>
       <c r="K13" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L13">
         <v>6</v>
@@ -845,8 +872,11 @@
       <c r="T13" t="s">
         <v>48</v>
       </c>
+      <c r="U13" t="s">
+        <v>33</v>
+      </c>
       <c r="V13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="X13">
         <v>1</v>
@@ -860,7 +890,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -872,7 +902,7 @@
         <v>-44</v>
       </c>
       <c r="G14" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="I14" t="s">
         <v>49</v>
@@ -895,7 +925,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -907,7 +937,7 @@
         <v>-39</v>
       </c>
       <c r="G15" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H15" t="s">
         <v>30</v>
@@ -919,7 +949,7 @@
         <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L15">
         <v>6</v>
@@ -932,6 +962,9 @@
       </c>
       <c r="T15" t="s">
         <v>52</v>
+      </c>
+      <c r="U15" t="s">
+        <v>36</v>
       </c>
       <c r="X15">
         <v>1</v>
@@ -945,7 +978,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -957,7 +990,7 @@
         <v>46</v>
       </c>
       <c r="G16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H16" t="s">
         <v>30</v>
@@ -969,7 +1002,7 @@
         <v>2</v>
       </c>
       <c r="K16" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L16">
         <v>7</v>
@@ -978,13 +1011,16 @@
         <v>32</v>
       </c>
       <c r="S16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T16" t="s">
         <v>53</v>
       </c>
+      <c r="U16" t="s">
+        <v>33</v>
+      </c>
       <c r="V16" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="X16">
         <v>1</v>
@@ -998,7 +1034,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1010,7 +1046,7 @@
         <v>44</v>
       </c>
       <c r="G17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H17" t="s">
         <v>30</v>
@@ -1022,7 +1058,7 @@
         <v>3</v>
       </c>
       <c r="K17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L17">
         <v>6</v>
@@ -1035,6 +1071,9 @@
       </c>
       <c r="T17" t="s">
         <v>55</v>
+      </c>
+      <c r="U17" t="s">
+        <v>36</v>
       </c>
       <c r="X17">
         <v>1</v>
@@ -1048,7 +1087,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -1060,7 +1099,7 @@
         <v>41</v>
       </c>
       <c r="G18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H18" t="s">
         <v>30</v>
@@ -1072,7 +1111,7 @@
         <v>6</v>
       </c>
       <c r="K18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L18">
         <v>5</v>
@@ -1085,6 +1124,9 @@
       </c>
       <c r="T18" t="s">
         <v>56</v>
+      </c>
+      <c r="U18" t="s">
+        <v>36</v>
       </c>
       <c r="X18">
         <v>1</v>
@@ -1098,7 +1140,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1110,10 +1152,10 @@
         <v>35</v>
       </c>
       <c r="G19" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I19" t="s">
         <v>57</v>
@@ -1122,7 +1164,7 @@
         <v>5</v>
       </c>
       <c r="K19" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L19">
         <v>6</v>
@@ -1138,6 +1180,9 @@
       </c>
       <c r="T19" t="s">
         <v>59</v>
+      </c>
+      <c r="U19" t="s">
+        <v>33</v>
       </c>
       <c r="X19">
         <v>1</v>
@@ -1172,10 +1217,13 @@
         <v>60</v>
       </c>
       <c r="K20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L20">
         <v>6</v>
+      </c>
+      <c r="U20" t="s">
+        <v>33</v>
       </c>
       <c r="X20">
         <v>2</v>
@@ -1189,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1213,19 +1261,22 @@
         <v>-5</v>
       </c>
       <c r="K21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L21">
         <v>6</v>
       </c>
       <c r="M21" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="S21" t="s">
         <v>50</v>
       </c>
       <c r="T21" t="s">
         <v>61</v>
+      </c>
+      <c r="U21" t="s">
+        <v>33</v>
       </c>
       <c r="X21">
         <v>3</v>
@@ -1239,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -1254,16 +1305,16 @@
         <v>26</v>
       </c>
       <c r="H22" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J22">
         <v>9</v>
       </c>
       <c r="K22" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L22">
         <v>6</v>
@@ -1279,6 +1330,9 @@
       </c>
       <c r="T22" t="s">
         <v>63</v>
+      </c>
+      <c r="U22" t="s">
+        <v>36</v>
       </c>
       <c r="X22">
         <v>3</v>
@@ -1292,7 +1346,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -1304,7 +1358,7 @@
         <v>18</v>
       </c>
       <c r="G23" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H23" t="s">
         <v>30</v>
@@ -1316,7 +1370,7 @@
         <v>18</v>
       </c>
       <c r="K23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L23">
         <v>6</v>
@@ -1325,13 +1379,16 @@
         <v>29</v>
       </c>
       <c r="S23" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T23" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="U23" t="s">
+        <v>33</v>
       </c>
       <c r="V23" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="X23">
         <v>3</v>
@@ -1357,7 +1414,7 @@
         <v>3</v>
       </c>
       <c r="G24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H24" t="s">
         <v>65</v>
@@ -1395,7 +1452,10 @@
         <v>27</v>
       </c>
       <c r="I25" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="X25">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1418,7 +1478,7 @@
         <v>-20</v>
       </c>
       <c r="G26" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H26" t="s">
         <v>30</v>
@@ -1434,6 +1494,12 @@
       </c>
       <c r="M26" t="s">
         <v>67</v>
+      </c>
+      <c r="U26" t="s">
+        <v>36</v>
+      </c>
+      <c r="X26">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1459,10 +1525,10 @@
         <v>26</v>
       </c>
       <c r="H27" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I27" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1475,6 +1541,12 @@
       </c>
       <c r="O27">
         <v>1</v>
+      </c>
+      <c r="U27" t="s">
+        <v>36</v>
+      </c>
+      <c r="X27">
+        <v>4</v>
       </c>
     </row>
     <row r="28">
@@ -1500,10 +1572,10 @@
         <v>26</v>
       </c>
       <c r="H28" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1516,6 +1588,12 @@
       </c>
       <c r="O28">
         <v>6</v>
+      </c>
+      <c r="U28" t="s">
+        <v>33</v>
+      </c>
+      <c r="X28">
+        <v>4</v>
       </c>
     </row>
     <row r="29">
@@ -1541,11 +1619,14 @@
         <v>26</v>
       </c>
       <c r="H29" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I29" t="s">
         <v>68</v>
       </c>
+      <c r="X29">
+        <v>4</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30">
@@ -1555,7 +1636,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1567,19 +1648,19 @@
         <v>-27</v>
       </c>
       <c r="G30" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H30" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I30" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L30">
         <v>7</v>
@@ -1591,11 +1672,17 @@
         <v>5</v>
       </c>
       <c r="S30" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T30" t="s">
         <v>69</v>
       </c>
+      <c r="U30" t="s">
+        <v>33</v>
+      </c>
+      <c r="X30">
+        <v>5</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31">
@@ -1605,7 +1692,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -1617,7 +1704,7 @@
         <v>-27</v>
       </c>
       <c r="G31" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H31" t="s">
         <v>30</v>
@@ -1629,7 +1716,7 @@
         <v>6</v>
       </c>
       <c r="K31" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L31">
         <v>6</v>
@@ -1642,6 +1729,12 @@
       </c>
       <c r="T31" t="s">
         <v>55</v>
+      </c>
+      <c r="U31" t="s">
+        <v>33</v>
+      </c>
+      <c r="X31">
+        <v>5</v>
       </c>
     </row>
     <row r="32">
@@ -1652,7 +1745,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D32">
         <v>3</v>
@@ -1664,7 +1757,7 @@
         <v>-33</v>
       </c>
       <c r="G32" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H32" t="s">
         <v>30</v>
@@ -1676,7 +1769,7 @@
         <v>67</v>
       </c>
       <c r="K32" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L32">
         <v>7</v>
@@ -1685,13 +1778,19 @@
         <v>29</v>
       </c>
       <c r="S32" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T32" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="U32" t="s">
+        <v>33</v>
       </c>
       <c r="V32" t="s">
-        <v>46</v>
+        <v>33</v>
+      </c>
+      <c r="X32">
+        <v>5</v>
       </c>
     </row>
     <row r="33">
@@ -1714,7 +1813,7 @@
         <v>3</v>
       </c>
       <c r="G33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H33" t="s">
         <v>65</v>
@@ -1722,6 +1821,9 @@
       <c r="I33" t="s">
         <v>66</v>
       </c>
+      <c r="X33">
+        <v>5</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34">
@@ -1750,6 +1852,9 @@
       </c>
       <c r="I34" t="s">
         <v>28</v>
+      </c>
+      <c r="X34">
+        <v>6</v>
       </c>
     </row>
     <row r="35">
@@ -1775,7 +1880,7 @@
         <v>26</v>
       </c>
       <c r="H35" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I35" t="s">
         <v>70</v>
@@ -1784,6 +1889,12 @@
         <v>4</v>
       </c>
       <c r="L35">
+        <v>6</v>
+      </c>
+      <c r="U35" t="s">
+        <v>36</v>
+      </c>
+      <c r="X35">
         <v>6</v>
       </c>
     </row>
@@ -1807,7 +1918,7 @@
         <v>-24</v>
       </c>
       <c r="G36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H36" t="s">
         <v>30</v>
@@ -1822,7 +1933,13 @@
         <v>5</v>
       </c>
       <c r="M36" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="U36" t="s">
+        <v>36</v>
+      </c>
+      <c r="X36">
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -1845,13 +1962,13 @@
         <v>-29</v>
       </c>
       <c r="G37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H37" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I37" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -1863,6 +1980,12 @@
         <v>12</v>
       </c>
       <c r="O37">
+        <v>6</v>
+      </c>
+      <c r="U37" t="s">
+        <v>33</v>
+      </c>
+      <c r="X37">
         <v>6</v>
       </c>
     </row>
@@ -1886,13 +2009,16 @@
         <v>-29</v>
       </c>
       <c r="G38" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H38" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I38" t="s">
         <v>71</v>
+      </c>
+      <c r="X38">
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -1903,7 +2029,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -1915,7 +2041,7 @@
         <v>-41</v>
       </c>
       <c r="G39" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H39" t="s">
         <v>30</v>
@@ -1927,7 +2053,7 @@
         <v>6</v>
       </c>
       <c r="K39" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L39">
         <v>7</v>
@@ -1939,13 +2065,19 @@
         <v>0</v>
       </c>
       <c r="S39" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T39" t="s">
         <v>72</v>
       </c>
+      <c r="U39" t="s">
+        <v>33</v>
+      </c>
       <c r="V39" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="X39">
+        <v>7</v>
       </c>
     </row>
     <row r="40">
@@ -1956,7 +2088,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -1968,19 +2100,19 @@
         <v>-47</v>
       </c>
       <c r="G40" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H40" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I40" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J40">
         <v>14</v>
       </c>
       <c r="K40" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L40">
         <v>6</v>
@@ -1996,6 +2128,12 @@
       </c>
       <c r="T40" t="s">
         <v>74</v>
+      </c>
+      <c r="U40" t="s">
+        <v>33</v>
+      </c>
+      <c r="X40">
+        <v>7</v>
       </c>
     </row>
     <row r="41">
@@ -2006,7 +2144,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2018,10 +2156,10 @@
         <v>39</v>
       </c>
       <c r="G41" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I41" t="s">
         <v>75</v>
@@ -2030,7 +2168,7 @@
         <v>39</v>
       </c>
       <c r="K41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L41">
         <v>6</v>
@@ -2046,6 +2184,12 @@
       </c>
       <c r="T41" t="s">
         <v>76</v>
+      </c>
+      <c r="U41" t="s">
+        <v>33</v>
+      </c>
+      <c r="X41">
+        <v>7</v>
       </c>
     </row>
     <row r="42">
@@ -2068,13 +2212,16 @@
         <v>3</v>
       </c>
       <c r="G42" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H42" t="s">
         <v>65</v>
       </c>
       <c r="I42" t="s">
         <v>66</v>
+      </c>
+      <c r="X42">
+        <v>7</v>
       </c>
     </row>
     <row r="43">
@@ -2103,7 +2250,10 @@
         <v>27</v>
       </c>
       <c r="I43" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="X43">
+        <v>8</v>
       </c>
     </row>
     <row r="44">
@@ -2129,10 +2279,10 @@
         <v>26</v>
       </c>
       <c r="H44" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I44" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J44">
         <v>11</v>
@@ -2145,6 +2295,12 @@
       </c>
       <c r="O44">
         <v>6</v>
+      </c>
+      <c r="U44" t="s">
+        <v>33</v>
+      </c>
+      <c r="X44">
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -2167,13 +2323,13 @@
         <v>-31</v>
       </c>
       <c r="G45" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H45" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I45" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J45">
         <v>-3</v>
@@ -2186,6 +2342,12 @@
       </c>
       <c r="O45">
         <v>2</v>
+      </c>
+      <c r="U45" t="s">
+        <v>36</v>
+      </c>
+      <c r="X45">
+        <v>8</v>
       </c>
     </row>
     <row r="46">
@@ -2211,10 +2373,10 @@
         <v>26</v>
       </c>
       <c r="H46" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I46" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -2227,6 +2389,12 @@
       </c>
       <c r="O46">
         <v>3</v>
+      </c>
+      <c r="U46" t="s">
+        <v>33</v>
+      </c>
+      <c r="X46">
+        <v>8</v>
       </c>
     </row>
     <row r="47">
@@ -2252,7 +2420,7 @@
         <v>26</v>
       </c>
       <c r="H47" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I47" t="s">
         <v>77</v>
@@ -2265,6 +2433,12 @@
       </c>
       <c r="O47">
         <v>6</v>
+      </c>
+      <c r="U47" t="s">
+        <v>33</v>
+      </c>
+      <c r="X47">
+        <v>8</v>
       </c>
     </row>
     <row r="48">
@@ -2295,6 +2469,9 @@
       <c r="I48" t="s">
         <v>66</v>
       </c>
+      <c r="X48">
+        <v>8</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49">
@@ -2324,6 +2501,9 @@
       <c r="I49" t="s">
         <v>28</v>
       </c>
+      <c r="X49">
+        <v>9</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50">
@@ -2362,6 +2542,12 @@
       <c r="M50" t="s">
         <v>51</v>
       </c>
+      <c r="U50" t="s">
+        <v>36</v>
+      </c>
+      <c r="X50">
+        <v>9</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51">
@@ -2386,10 +2572,10 @@
         <v>26</v>
       </c>
       <c r="H51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I51" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -2402,6 +2588,12 @@
       </c>
       <c r="O51">
         <v>5</v>
+      </c>
+      <c r="U51" t="s">
+        <v>36</v>
+      </c>
+      <c r="X51">
+        <v>9</v>
       </c>
     </row>
     <row r="52">
@@ -2427,7 +2619,7 @@
         <v>26</v>
       </c>
       <c r="H52" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I52" t="s">
         <v>70</v>
@@ -2437,6 +2629,12 @@
       </c>
       <c r="L52">
         <v>5</v>
+      </c>
+      <c r="U52" t="s">
+        <v>33</v>
+      </c>
+      <c r="X52">
+        <v>9</v>
       </c>
     </row>
     <row r="53">
@@ -2462,10 +2660,13 @@
         <v>26</v>
       </c>
       <c r="H53" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I53" t="s">
         <v>68</v>
+      </c>
+      <c r="X53">
+        <v>9</v>
       </c>
     </row>
     <row r="54">
@@ -2476,7 +2677,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2488,19 +2689,19 @@
         <v>39</v>
       </c>
       <c r="G54" t="s">
+        <v>36</v>
+      </c>
+      <c r="H54" t="s">
+        <v>34</v>
+      </c>
+      <c r="I54" t="s">
         <v>35</v>
-      </c>
-      <c r="H54" t="s">
-        <v>33</v>
-      </c>
-      <c r="I54" t="s">
-        <v>34</v>
       </c>
       <c r="J54">
         <v>13</v>
       </c>
       <c r="K54" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L54">
         <v>6</v>
@@ -2516,6 +2717,12 @@
       </c>
       <c r="T54" t="s">
         <v>52</v>
+      </c>
+      <c r="U54" t="s">
+        <v>33</v>
+      </c>
+      <c r="X54">
+        <v>10</v>
       </c>
     </row>
     <row r="55">
@@ -2526,7 +2733,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2538,7 +2745,7 @@
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H55" t="s">
         <v>30</v>
@@ -2550,7 +2757,7 @@
         <v>12</v>
       </c>
       <c r="K55" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L55">
         <v>6</v>
@@ -2559,13 +2766,19 @@
         <v>32</v>
       </c>
       <c r="S55" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T55" t="s">
         <v>72</v>
       </c>
+      <c r="U55" t="s">
+        <v>33</v>
+      </c>
       <c r="V55" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="X55">
+        <v>10</v>
       </c>
     </row>
     <row r="56">
@@ -2576,7 +2789,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2588,7 +2801,7 @@
         <v>14</v>
       </c>
       <c r="G56" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H56" t="s">
         <v>30</v>
@@ -2600,7 +2813,7 @@
         <v>9</v>
       </c>
       <c r="K56" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L56">
         <v>6</v>
@@ -2613,6 +2826,12 @@
       </c>
       <c r="T56" t="s">
         <v>78</v>
+      </c>
+      <c r="U56" t="s">
+        <v>36</v>
+      </c>
+      <c r="X56">
+        <v>10</v>
       </c>
     </row>
     <row r="57">
@@ -2623,7 +2842,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -2647,7 +2866,7 @@
         <v>4</v>
       </c>
       <c r="K57" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L57">
         <v>6</v>
@@ -2659,7 +2878,13 @@
         <v>47</v>
       </c>
       <c r="T57" t="s">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="U57" t="s">
+        <v>33</v>
+      </c>
+      <c r="X57">
+        <v>10</v>
       </c>
     </row>
     <row r="58">
@@ -2670,7 +2895,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2682,7 +2907,7 @@
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H58" t="s">
         <v>30</v>
@@ -2694,7 +2919,7 @@
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L58">
         <v>9</v>
@@ -2707,6 +2932,12 @@
       </c>
       <c r="T58" t="s">
         <v>69</v>
+      </c>
+      <c r="U58" t="s">
+        <v>33</v>
+      </c>
+      <c r="X58">
+        <v>10</v>
       </c>
     </row>
     <row r="59">
@@ -2737,6 +2968,9 @@
       <c r="I59" t="s">
         <v>66</v>
       </c>
+      <c r="X59">
+        <v>10</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60">
@@ -2754,6 +2988,9 @@
       <c r="E60">
         <v>10</v>
       </c>
+      <c r="F60">
+        <v>-40</v>
+      </c>
       <c r="G60" t="s">
         <v>26</v>
       </c>
@@ -2761,7 +2998,10 @@
         <v>27</v>
       </c>
       <c r="I60" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="X60">
+        <v>11</v>
       </c>
     </row>
     <row r="61">
@@ -2801,6 +3041,12 @@
       <c r="M61" t="s">
         <v>51</v>
       </c>
+      <c r="U61" t="s">
+        <v>33</v>
+      </c>
+      <c r="X61">
+        <v>11</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62">
@@ -2839,6 +3085,12 @@
       <c r="M62" t="s">
         <v>32</v>
       </c>
+      <c r="U62" t="s">
+        <v>33</v>
+      </c>
+      <c r="X62">
+        <v>11</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63">
@@ -2860,10 +3112,10 @@
         <v>-18</v>
       </c>
       <c r="G63" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H63" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I63" t="s">
         <v>77</v>
@@ -2876,6 +3128,12 @@
       </c>
       <c r="O63">
         <v>1</v>
+      </c>
+      <c r="U63" t="s">
+        <v>36</v>
+      </c>
+      <c r="X63">
+        <v>11</v>
       </c>
     </row>
     <row r="64">
@@ -2898,13 +3156,16 @@
         <v>3</v>
       </c>
       <c r="G64" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H64" t="s">
         <v>65</v>
       </c>
       <c r="I64" t="s">
         <v>66</v>
+      </c>
+      <c r="X64">
+        <v>11</v>
       </c>
     </row>
     <row r="65">
@@ -2933,7 +3194,10 @@
         <v>27</v>
       </c>
       <c r="I65" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="X65">
+        <v>12</v>
       </c>
     </row>
     <row r="66">
@@ -2959,10 +3223,10 @@
         <v>26</v>
       </c>
       <c r="H66" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I66" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J66">
         <v>11</v>
@@ -2975,6 +3239,12 @@
       </c>
       <c r="O66">
         <v>2</v>
+      </c>
+      <c r="U66" t="s">
+        <v>33</v>
+      </c>
+      <c r="X66">
+        <v>12</v>
       </c>
     </row>
     <row r="67">
@@ -2997,7 +3267,7 @@
         <v>-36</v>
       </c>
       <c r="G67" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H67" t="s">
         <v>30</v>
@@ -3013,6 +3283,12 @@
       </c>
       <c r="M67" t="s">
         <v>51</v>
+      </c>
+      <c r="U67" t="s">
+        <v>36</v>
+      </c>
+      <c r="X67">
+        <v>12</v>
       </c>
     </row>
     <row r="68">
@@ -3035,10 +3311,10 @@
         <v>-39</v>
       </c>
       <c r="G68" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H68" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I68" t="s">
         <v>80</v>
@@ -3051,6 +3327,12 @@
       </c>
       <c r="O68">
         <v>2</v>
+      </c>
+      <c r="U68" t="s">
+        <v>36</v>
+      </c>
+      <c r="X68">
+        <v>12</v>
       </c>
     </row>
     <row r="69">
@@ -3073,13 +3355,16 @@
         <v>3</v>
       </c>
       <c r="G69" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H69" t="s">
         <v>65</v>
       </c>
       <c r="I69" t="s">
         <v>66</v>
+      </c>
+      <c r="X69">
+        <v>12</v>
       </c>
     </row>
     <row r="70">
@@ -3108,7 +3393,10 @@
         <v>27</v>
       </c>
       <c r="I70" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="X70">
+        <v>13</v>
       </c>
     </row>
     <row r="71">
@@ -3131,7 +3419,7 @@
         <v>-35</v>
       </c>
       <c r="G71" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H71" t="s">
         <v>30</v>
@@ -3147,6 +3435,12 @@
       </c>
       <c r="M71" t="s">
         <v>32</v>
+      </c>
+      <c r="U71" t="s">
+        <v>33</v>
+      </c>
+      <c r="X71">
+        <v>13</v>
       </c>
     </row>
     <row r="72">
@@ -3169,13 +3463,13 @@
         <v>-37</v>
       </c>
       <c r="G72" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H72" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I72" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -3188,6 +3482,12 @@
       </c>
       <c r="O72">
         <v>9</v>
+      </c>
+      <c r="U72" t="s">
+        <v>33</v>
+      </c>
+      <c r="X72">
+        <v>13</v>
       </c>
     </row>
     <row r="73">
@@ -3210,7 +3510,7 @@
         <v>-37</v>
       </c>
       <c r="G73" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H73" t="s">
         <v>30</v>
@@ -3226,6 +3526,12 @@
       </c>
       <c r="M73" t="s">
         <v>51</v>
+      </c>
+      <c r="U73" t="s">
+        <v>33</v>
+      </c>
+      <c r="X73">
+        <v>13</v>
       </c>
     </row>
     <row r="74">
@@ -3248,13 +3554,16 @@
         <v>-40</v>
       </c>
       <c r="G74" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H74" t="s">
         <v>81</v>
       </c>
       <c r="I74" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="X74">
+        <v>13</v>
       </c>
     </row>
     <row r="75">
@@ -3265,7 +3574,7 @@
         <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3277,19 +3586,19 @@
         <v>-25</v>
       </c>
       <c r="G75" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H75" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I75" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J75">
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L75">
         <v>6</v>
@@ -3305,6 +3614,12 @@
       </c>
       <c r="T75" t="s">
         <v>59</v>
+      </c>
+      <c r="U75" t="s">
+        <v>36</v>
+      </c>
+      <c r="X75">
+        <v>13</v>
       </c>
     </row>
     <row r="76">
@@ -3315,7 +3630,7 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -3327,7 +3642,7 @@
         <v>-25</v>
       </c>
       <c r="G76" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H76" t="s">
         <v>30</v>
@@ -3339,7 +3654,7 @@
         <v>20</v>
       </c>
       <c r="K76" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L76">
         <v>6</v>
@@ -3352,6 +3667,12 @@
       </c>
       <c r="T76" t="s">
         <v>82</v>
+      </c>
+      <c r="U76" t="s">
+        <v>33</v>
+      </c>
+      <c r="X76">
+        <v>13</v>
       </c>
     </row>
     <row r="77">
@@ -3362,7 +3683,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3374,19 +3695,19 @@
         <v>-45</v>
       </c>
       <c r="G77" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H77" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I77" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J77">
         <v>4</v>
       </c>
       <c r="K77" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L77">
         <v>8</v>
@@ -3398,10 +3719,16 @@
         <v>1</v>
       </c>
       <c r="S77" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T77" t="s">
         <v>83</v>
+      </c>
+      <c r="U77" t="s">
+        <v>36</v>
+      </c>
+      <c r="X77">
+        <v>13</v>
       </c>
     </row>
     <row r="78">
@@ -3412,7 +3739,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -3424,19 +3751,19 @@
         <v>-49</v>
       </c>
       <c r="G78" t="s">
+        <v>36</v>
+      </c>
+      <c r="H78" t="s">
+        <v>34</v>
+      </c>
+      <c r="I78" t="s">
         <v>35</v>
-      </c>
-      <c r="H78" t="s">
-        <v>33</v>
-      </c>
-      <c r="I78" t="s">
-        <v>34</v>
       </c>
       <c r="J78">
         <v>8</v>
       </c>
       <c r="K78" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L78">
         <v>6</v>
@@ -3452,6 +3779,12 @@
       </c>
       <c r="T78" t="s">
         <v>82</v>
+      </c>
+      <c r="U78" t="s">
+        <v>36</v>
+      </c>
+      <c r="X78">
+        <v>13</v>
       </c>
     </row>
     <row r="79">
@@ -3462,7 +3795,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3474,7 +3807,7 @@
         <v>43</v>
       </c>
       <c r="G79" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H79" t="s">
         <v>30</v>
@@ -3486,7 +3819,7 @@
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L79">
         <v>7</v>
@@ -3499,6 +3832,12 @@
       </c>
       <c r="T79" t="s">
         <v>55</v>
+      </c>
+      <c r="U79" t="s">
+        <v>36</v>
+      </c>
+      <c r="X79">
+        <v>13</v>
       </c>
     </row>
     <row r="80">
@@ -3509,7 +3848,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D80">
         <v>2</v>
@@ -3521,19 +3860,19 @@
         <v>41</v>
       </c>
       <c r="G80" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H80" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I80" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J80">
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L80">
         <v>7</v>
@@ -3545,10 +3884,16 @@
         <v>6</v>
       </c>
       <c r="S80" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T80" t="s">
         <v>84</v>
+      </c>
+      <c r="U80" t="s">
+        <v>33</v>
+      </c>
+      <c r="X80">
+        <v>13</v>
       </c>
     </row>
     <row r="81">
@@ -3559,7 +3904,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D81">
         <v>3</v>
@@ -3571,19 +3916,19 @@
         <v>41</v>
       </c>
       <c r="G81" t="s">
+        <v>36</v>
+      </c>
+      <c r="H81" t="s">
+        <v>34</v>
+      </c>
+      <c r="I81" t="s">
         <v>35</v>
-      </c>
-      <c r="H81" t="s">
-        <v>33</v>
-      </c>
-      <c r="I81" t="s">
-        <v>34</v>
       </c>
       <c r="J81">
         <v>11</v>
       </c>
       <c r="K81" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L81">
         <v>6</v>
@@ -3599,6 +3944,12 @@
       </c>
       <c r="T81" t="s">
         <v>85</v>
+      </c>
+      <c r="U81" t="s">
+        <v>33</v>
+      </c>
+      <c r="X81">
+        <v>13</v>
       </c>
     </row>
     <row r="82">
@@ -3609,7 +3960,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3621,19 +3972,19 @@
         <v>30</v>
       </c>
       <c r="G82" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H82" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I82" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L82">
         <v>5</v>
@@ -3649,6 +4000,9 @@
       </c>
       <c r="T82" t="s">
         <v>59</v>
+      </c>
+      <c r="U82" t="s">
+        <v>36</v>
       </c>
       <c r="X82">
         <v>9</v>
@@ -3662,7 +4016,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -3674,7 +4028,7 @@
         <v>30</v>
       </c>
       <c r="G83" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H83" t="s">
         <v>30</v>
@@ -3690,6 +4044,9 @@
       </c>
       <c r="T83" t="s">
         <v>82</v>
+      </c>
+      <c r="U83" t="s">
+        <v>36</v>
       </c>
       <c r="X83">
         <v>9</v>
@@ -3703,7 +4060,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -3715,19 +4072,19 @@
         <v>38</v>
       </c>
       <c r="G84" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H84" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I84" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J84">
         <v>8</v>
       </c>
       <c r="K84" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L84">
         <v>6</v>
@@ -3743,6 +4100,9 @@
       </c>
       <c r="T84" t="s">
         <v>86</v>
+      </c>
+      <c r="U84" t="s">
+        <v>33</v>
       </c>
       <c r="X84">
         <v>9</v>
@@ -3756,7 +4116,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D85">
         <v>3</v>
@@ -3768,7 +4128,7 @@
         <v>30</v>
       </c>
       <c r="G85" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H85" t="s">
         <v>30</v>
@@ -3780,7 +4140,7 @@
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L85">
         <v>7</v>
@@ -3789,10 +4149,13 @@
         <v>32</v>
       </c>
       <c r="S85" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="T85" t="s">
         <v>52</v>
+      </c>
+      <c r="U85" t="s">
+        <v>36</v>
       </c>
       <c r="X85">
         <v>9</v>
@@ -3806,7 +4169,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D86">
         <v>4</v>
@@ -3818,10 +4181,10 @@
         <v>29</v>
       </c>
       <c r="G86" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H86" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I86" t="s">
         <v>75</v>
@@ -3830,7 +4193,7 @@
         <v>29</v>
       </c>
       <c r="K86" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L86">
         <v>7</v>
@@ -3846,6 +4209,9 @@
       </c>
       <c r="T86" t="s">
         <v>86</v>
+      </c>
+      <c r="U86" t="s">
+        <v>36</v>
       </c>
       <c r="X86">
         <v>9</v>
@@ -3871,7 +4237,7 @@
         <v>3</v>
       </c>
       <c r="G87" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H87" t="s">
         <v>65</v>
@@ -3909,7 +4275,10 @@
         <v>27</v>
       </c>
       <c r="I88" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="X88">
+        <v>10</v>
       </c>
     </row>
     <row r="89">
@@ -3932,7 +4301,7 @@
         <v>-24</v>
       </c>
       <c r="G89" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H89" t="s">
         <v>30</v>
@@ -3947,7 +4316,13 @@
         <v>6</v>
       </c>
       <c r="M89" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="U89" t="s">
+        <v>33</v>
+      </c>
+      <c r="X89">
+        <v>10</v>
       </c>
     </row>
     <row r="90">
@@ -3970,7 +4345,7 @@
         <v>-32</v>
       </c>
       <c r="G90" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H90" t="s">
         <v>30</v>
@@ -3986,6 +4361,12 @@
       </c>
       <c r="M90" t="s">
         <v>32</v>
+      </c>
+      <c r="U90" t="s">
+        <v>36</v>
+      </c>
+      <c r="X90">
+        <v>10</v>
       </c>
     </row>
     <row r="91">
@@ -4008,7 +4389,7 @@
         <v>-38</v>
       </c>
       <c r="G91" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H91" t="s">
         <v>30</v>
@@ -4024,6 +4405,12 @@
       </c>
       <c r="M91" t="s">
         <v>51</v>
+      </c>
+      <c r="U91" t="s">
+        <v>33</v>
+      </c>
+      <c r="X91">
+        <v>10</v>
       </c>
     </row>
     <row r="92">
@@ -4046,7 +4433,7 @@
         <v>-42</v>
       </c>
       <c r="G92" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H92" t="s">
         <v>30</v>
@@ -4061,7 +4448,13 @@
         <v>5</v>
       </c>
       <c r="M92" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="U92" t="s">
+        <v>33</v>
+      </c>
+      <c r="X92">
+        <v>10</v>
       </c>
     </row>
     <row r="93">
@@ -4084,7 +4477,7 @@
         <v>-46</v>
       </c>
       <c r="G93" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H93" t="s">
         <v>30</v>
@@ -4100,6 +4493,12 @@
       </c>
       <c r="M93" t="s">
         <v>32</v>
+      </c>
+      <c r="U93" t="s">
+        <v>33</v>
+      </c>
+      <c r="X93">
+        <v>10</v>
       </c>
     </row>
     <row r="94">
@@ -4122,7 +4521,7 @@
         <v>48</v>
       </c>
       <c r="G94" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H94" t="s">
         <v>30</v>
@@ -4138,6 +4537,12 @@
       </c>
       <c r="M94" t="s">
         <v>51</v>
+      </c>
+      <c r="U94" t="s">
+        <v>36</v>
+      </c>
+      <c r="X94">
+        <v>10</v>
       </c>
     </row>
     <row r="95">
@@ -4163,10 +4568,10 @@
         <v>26</v>
       </c>
       <c r="H95" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I95" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -4179,6 +4584,12 @@
       </c>
       <c r="O95">
         <v>3</v>
+      </c>
+      <c r="U95" t="s">
+        <v>33</v>
+      </c>
+      <c r="X95">
+        <v>10</v>
       </c>
     </row>
     <row r="96">
@@ -4216,7 +4627,13 @@
         <v>5</v>
       </c>
       <c r="M96" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="U96" t="s">
+        <v>36</v>
+      </c>
+      <c r="X96">
+        <v>10</v>
       </c>
     </row>
     <row r="97">
@@ -4256,6 +4673,12 @@
       <c r="M97" t="s">
         <v>51</v>
       </c>
+      <c r="U97" t="s">
+        <v>33</v>
+      </c>
+      <c r="X97">
+        <v>10</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98">
@@ -4294,6 +4717,12 @@
       <c r="M98" t="s">
         <v>32</v>
       </c>
+      <c r="U98" t="s">
+        <v>33</v>
+      </c>
+      <c r="X98">
+        <v>10</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99">
@@ -4318,10 +4747,10 @@
         <v>26</v>
       </c>
       <c r="H99" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I99" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -4334,6 +4763,12 @@
       </c>
       <c r="O99">
         <v>9</v>
+      </c>
+      <c r="U99" t="s">
+        <v>33</v>
+      </c>
+      <c r="X99">
+        <v>10</v>
       </c>
     </row>
     <row r="100">
@@ -4373,6 +4808,12 @@
       <c r="M100" t="s">
         <v>32</v>
       </c>
+      <c r="U100" t="s">
+        <v>36</v>
+      </c>
+      <c r="X100">
+        <v>10</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101">
@@ -4394,7 +4835,7 @@
         <v>29</v>
       </c>
       <c r="G101" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H101" t="s">
         <v>30</v>
@@ -4410,6 +4851,12 @@
       </c>
       <c r="M101" t="s">
         <v>32</v>
+      </c>
+      <c r="U101" t="s">
+        <v>36</v>
+      </c>
+      <c r="X101">
+        <v>10</v>
       </c>
     </row>
     <row r="102">
@@ -4432,7 +4879,7 @@
         <v>22</v>
       </c>
       <c r="G102" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H102" t="s">
         <v>30</v>
@@ -4448,6 +4895,12 @@
       </c>
       <c r="M102" t="s">
         <v>51</v>
+      </c>
+      <c r="U102" t="s">
+        <v>33</v>
+      </c>
+      <c r="X102">
+        <v>10</v>
       </c>
     </row>
     <row r="103">
@@ -4470,7 +4923,7 @@
         <v>20</v>
       </c>
       <c r="G103" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H103" t="s">
         <v>30</v>
@@ -4486,6 +4939,12 @@
       </c>
       <c r="M103" t="s">
         <v>32</v>
+      </c>
+      <c r="U103" t="s">
+        <v>36</v>
+      </c>
+      <c r="X103">
+        <v>10</v>
       </c>
     </row>
     <row r="104">
@@ -4496,7 +4955,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -4508,7 +4967,7 @@
         <v>-18</v>
       </c>
       <c r="G104" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H104" t="s">
         <v>30</v>
@@ -4524,6 +4983,12 @@
       </c>
       <c r="M104" t="s">
         <v>51</v>
+      </c>
+      <c r="U104" t="s">
+        <v>33</v>
+      </c>
+      <c r="X104">
+        <v>11</v>
       </c>
     </row>
     <row r="105">
@@ -4534,7 +4999,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -4546,7 +5011,7 @@
         <v>-19</v>
       </c>
       <c r="G105" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H105" t="s">
         <v>30</v>
@@ -4558,13 +5023,19 @@
         <v>4</v>
       </c>
       <c r="K105" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L105">
         <v>6</v>
       </c>
       <c r="M105" t="s">
         <v>29</v>
+      </c>
+      <c r="U105" t="s">
+        <v>33</v>
+      </c>
+      <c r="X105">
+        <v>11</v>
       </c>
     </row>
     <row r="106">
@@ -4575,7 +5046,7 @@
         <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -4587,7 +5058,7 @@
         <v>-23</v>
       </c>
       <c r="G106" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H106" t="s">
         <v>30</v>
@@ -4603,6 +5074,12 @@
       </c>
       <c r="M106" t="s">
         <v>51</v>
+      </c>
+      <c r="U106" t="s">
+        <v>33</v>
+      </c>
+      <c r="X106">
+        <v>11</v>
       </c>
     </row>
     <row r="107">
@@ -4625,13 +5102,16 @@
         <v>-26</v>
       </c>
       <c r="G107" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="H107" t="s">
         <v>88</v>
       </c>
       <c r="I107" t="s">
         <v>68</v>
+      </c>
+      <c r="X107">
+        <v>11</v>
       </c>
     </row>
     <row r="108">
@@ -4669,7 +5149,13 @@
         <v>5</v>
       </c>
       <c r="M108" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="U108" t="s">
+        <v>36</v>
+      </c>
+      <c r="X108">
+        <v>12</v>
       </c>
     </row>
     <row r="109">
@@ -4695,7 +5181,7 @@
         <v>26</v>
       </c>
       <c r="H109" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I109" t="s">
         <v>89</v>
@@ -4705,6 +5191,9 @@
       </c>
       <c r="L109">
         <v>6</v>
+      </c>
+      <c r="X109">
+        <v>12</v>
       </c>
     </row>
     <row r="110">
@@ -4727,7 +5216,7 @@
         <v>-34</v>
       </c>
       <c r="G110" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H110" t="s">
         <v>30</v>
@@ -4742,7 +5231,13 @@
         <v>6</v>
       </c>
       <c r="M110" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="U110" t="s">
+        <v>36</v>
+      </c>
+      <c r="X110">
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/Dowling/dowling-vs-waterloo-west-092526.xlsx
+++ b/Dowling/dowling-vs-waterloo-west-092526.xlsx
@@ -5,7 +5,7 @@
     <workbookView/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="R526acbb4b78e47dd"/>
+    <sheet name="Sheet1" sheetId="1" r:id="R75b3bf112151414d"/>
   </sheets>
 </workbook>
 </file>
@@ -58,6 +58,21 @@
     <t>PASS ZONE</t>
   </si>
   <si>
+    <t>BACKFIELD</t>
+  </si>
+  <si>
+    <t>DEF FRONT</t>
+  </si>
+  <si>
+    <t>FRONT MOVEMENT</t>
+  </si>
+  <si>
+    <t>COVERAGE</t>
+  </si>
+  <si>
+    <t>BLITZ</t>
+  </si>
+  <si>
     <t>KICK YARDS</t>
   </si>
   <si>
@@ -77,9 +92,6 @@
   </si>
   <si>
     <t>MOTION DIR</t>
-  </si>
-  <si>
-    <t>COVERAGE</t>
   </si>
   <si>
     <t>SERIES</t>
@@ -287,7 +299,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y110"/>
+  <dimension ref="A1:AC110"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
@@ -365,6 +377,18 @@
       <c r="Y1" t="s">
         <v>24</v>
       </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2">
@@ -374,7 +398,7 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -386,13 +410,13 @@
         <v>-40</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H2" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I2" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -403,7 +427,7 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -415,13 +439,13 @@
         <v>-20</v>
       </c>
       <c r="G3" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H3" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I3" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -430,10 +454,10 @@
         <v>5</v>
       </c>
       <c r="M3" t="s">
-        <v>32</v>
-      </c>
-      <c r="U3" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -444,7 +468,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -456,13 +480,13 @@
         <v>-21</v>
       </c>
       <c r="G4" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H4" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J4">
         <v>10</v>
@@ -476,8 +500,8 @@
       <c r="O4">
         <v>1</v>
       </c>
-      <c r="U4" t="s">
-        <v>36</v>
+      <c r="Z4" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -488,7 +512,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -500,13 +524,13 @@
         <v>-31</v>
       </c>
       <c r="G5" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -515,10 +539,10 @@
         <v>6</v>
       </c>
       <c r="M5" t="s">
-        <v>37</v>
-      </c>
-      <c r="U5" t="s">
-        <v>36</v>
+        <v>41</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -529,7 +553,7 @@
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D6">
         <v>2</v>
@@ -541,13 +565,13 @@
         <v>-32</v>
       </c>
       <c r="G6" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I6" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J6">
         <v>22</v>
@@ -561,8 +585,8 @@
       <c r="O6">
         <v>4</v>
       </c>
-      <c r="U6" t="s">
-        <v>36</v>
+      <c r="Z6" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -573,7 +597,7 @@
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -585,13 +609,13 @@
         <v>46</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I7" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J7">
         <v>-2</v>
@@ -600,10 +624,10 @@
         <v>6</v>
       </c>
       <c r="M7" t="s">
-        <v>32</v>
-      </c>
-      <c r="U7" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="8">
@@ -614,7 +638,7 @@
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D8">
         <v>2</v>
@@ -626,13 +650,13 @@
         <v>48</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H8" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I8" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -641,10 +665,10 @@
         <v>6</v>
       </c>
       <c r="M8" t="s">
-        <v>32</v>
-      </c>
-      <c r="U8" t="s">
-        <v>33</v>
+        <v>36</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="9">
@@ -655,7 +679,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D9">
         <v>3</v>
@@ -667,13 +691,13 @@
         <v>48</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I9" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -687,8 +711,8 @@
       <c r="O9">
         <v>4</v>
       </c>
-      <c r="U9" t="s">
-        <v>36</v>
+      <c r="Z9" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="10">
@@ -699,7 +723,7 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D10">
         <v>4</v>
@@ -711,15 +735,15 @@
         <v>48</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H10" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I10" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q10">
+        <v>44</v>
+      </c>
+      <c r="V10">
         <v>15</v>
       </c>
     </row>
@@ -731,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="C11" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D11">
         <v>1</v>
@@ -743,19 +767,19 @@
         <v>-29</v>
       </c>
       <c r="G11" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H11" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J11">
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L11">
         <v>7</v>
@@ -766,14 +790,14 @@
       <c r="O11">
         <v>9</v>
       </c>
-      <c r="S11" t="s">
-        <v>43</v>
-      </c>
-      <c r="T11" t="s">
-        <v>44</v>
-      </c>
-      <c r="U11" t="s">
-        <v>33</v>
+      <c r="X11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>48</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -784,7 +808,7 @@
         <v>1</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D12">
         <v>2</v>
@@ -796,34 +820,34 @@
         <v>-29</v>
       </c>
       <c r="G12" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H12" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I12" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J12">
         <v>8</v>
       </c>
       <c r="K12" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L12">
         <v>7</v>
       </c>
       <c r="M12" t="s">
-        <v>29</v>
-      </c>
-      <c r="S12" t="s">
-        <v>43</v>
-      </c>
-      <c r="T12" t="s">
-        <v>46</v>
-      </c>
-      <c r="U12" t="s">
-        <v>33</v>
+        <v>33</v>
+      </c>
+      <c r="X12" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -834,7 +858,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D13">
         <v>3</v>
@@ -846,39 +870,39 @@
         <v>-37</v>
       </c>
       <c r="G13" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I13" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J13">
         <v>7</v>
       </c>
       <c r="K13" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L13">
         <v>6</v>
       </c>
       <c r="M13" t="s">
-        <v>29</v>
-      </c>
-      <c r="S13" t="s">
-        <v>47</v>
-      </c>
-      <c r="T13" t="s">
-        <v>48</v>
-      </c>
-      <c r="U13" t="s">
-        <v>33</v>
-      </c>
-      <c r="V13" t="s">
-        <v>36</v>
-      </c>
-      <c r="X13">
+        <v>33</v>
+      </c>
+      <c r="X13" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y13" t="s">
+        <v>52</v>
+      </c>
+      <c r="Z13" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA13" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB13">
         <v>1</v>
       </c>
     </row>
@@ -890,7 +914,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D14">
         <v>1</v>
@@ -902,18 +926,18 @@
         <v>-44</v>
       </c>
       <c r="G14" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I14" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J14">
         <v>-5</v>
       </c>
-      <c r="S14" t="s">
-        <v>50</v>
-      </c>
-      <c r="X14">
+      <c r="X14" t="s">
+        <v>54</v>
+      </c>
+      <c r="AB14">
         <v>1</v>
       </c>
     </row>
@@ -925,7 +949,7 @@
         <v>1</v>
       </c>
       <c r="C15" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D15">
         <v>1</v>
@@ -937,36 +961,36 @@
         <v>-39</v>
       </c>
       <c r="G15" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H15" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I15" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J15">
         <v>15</v>
       </c>
       <c r="K15" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L15">
         <v>6</v>
       </c>
       <c r="M15" t="s">
+        <v>55</v>
+      </c>
+      <c r="X15" t="s">
         <v>51</v>
       </c>
-      <c r="S15" t="s">
-        <v>47</v>
-      </c>
-      <c r="T15" t="s">
-        <v>52</v>
-      </c>
-      <c r="U15" t="s">
-        <v>36</v>
-      </c>
-      <c r="X15">
+      <c r="Y15" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z15" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB15">
         <v>1</v>
       </c>
     </row>
@@ -978,7 +1002,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D16">
         <v>1</v>
@@ -990,39 +1014,39 @@
         <v>46</v>
       </c>
       <c r="G16" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H16" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I16" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J16">
         <v>2</v>
       </c>
       <c r="K16" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L16">
         <v>7</v>
       </c>
       <c r="M16" t="s">
-        <v>32</v>
-      </c>
-      <c r="S16" t="s">
-        <v>43</v>
-      </c>
-      <c r="T16" t="s">
-        <v>53</v>
-      </c>
-      <c r="U16" t="s">
-        <v>33</v>
-      </c>
-      <c r="V16" t="s">
-        <v>33</v>
-      </c>
-      <c r="X16">
+        <v>36</v>
+      </c>
+      <c r="X16" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>57</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB16">
         <v>1</v>
       </c>
     </row>
@@ -1034,7 +1058,7 @@
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D17">
         <v>2</v>
@@ -1046,36 +1070,36 @@
         <v>44</v>
       </c>
       <c r="G17" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H17" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I17" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J17">
         <v>3</v>
       </c>
       <c r="K17" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L17">
         <v>6</v>
       </c>
       <c r="M17" t="s">
-        <v>51</v>
-      </c>
-      <c r="S17" t="s">
-        <v>54</v>
-      </c>
-      <c r="T17" t="s">
         <v>55</v>
       </c>
-      <c r="U17" t="s">
-        <v>36</v>
-      </c>
-      <c r="X17">
+      <c r="X17" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y17" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z17" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB17">
         <v>1</v>
       </c>
     </row>
@@ -1087,7 +1111,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D18">
         <v>3</v>
@@ -1099,36 +1123,39 @@
         <v>41</v>
       </c>
       <c r="G18" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H18" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I18" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J18">
         <v>6</v>
       </c>
       <c r="K18" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L18">
         <v>5</v>
       </c>
       <c r="M18" t="s">
-        <v>32</v>
-      </c>
-      <c r="S18" t="s">
-        <v>50</v>
-      </c>
-      <c r="T18" t="s">
-        <v>56</v>
-      </c>
-      <c r="U18" t="s">
         <v>36</v>
       </c>
-      <c r="X18">
+      <c r="P18" t="s">
+        <v>29</v>
+      </c>
+      <c r="X18" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>60</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB18">
         <v>1</v>
       </c>
     </row>
@@ -1140,7 +1167,7 @@
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D19">
         <v>1</v>
@@ -1152,19 +1179,19 @@
         <v>35</v>
       </c>
       <c r="G19" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H19" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I19" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J19">
         <v>5</v>
       </c>
       <c r="K19" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L19">
         <v>6</v>
@@ -1175,16 +1202,16 @@
       <c r="O19">
         <v>2</v>
       </c>
-      <c r="S19" t="s">
-        <v>58</v>
-      </c>
-      <c r="T19" t="s">
-        <v>59</v>
-      </c>
-      <c r="U19" t="s">
-        <v>33</v>
-      </c>
-      <c r="X19">
+      <c r="X19" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB19">
         <v>1</v>
       </c>
     </row>
@@ -1196,7 +1223,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D20">
         <v>1</v>
@@ -1208,24 +1235,24 @@
         <v>-31</v>
       </c>
       <c r="G20" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I20" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="K20" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L20">
         <v>6</v>
       </c>
-      <c r="U20" t="s">
-        <v>33</v>
-      </c>
-      <c r="X20">
+      <c r="Z20" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB20">
         <v>2</v>
       </c>
     </row>
@@ -1237,7 +1264,7 @@
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D21">
         <v>1</v>
@@ -1249,36 +1276,36 @@
         <v>22</v>
       </c>
       <c r="G21" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H21" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I21" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J21">
         <v>-5</v>
       </c>
       <c r="K21" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L21">
         <v>6</v>
       </c>
       <c r="M21" t="s">
-        <v>37</v>
-      </c>
-      <c r="S21" t="s">
-        <v>50</v>
-      </c>
-      <c r="T21" t="s">
-        <v>61</v>
-      </c>
-      <c r="U21" t="s">
-        <v>33</v>
-      </c>
-      <c r="X21">
+        <v>41</v>
+      </c>
+      <c r="X21" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y21" t="s">
+        <v>65</v>
+      </c>
+      <c r="Z21" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB21">
         <v>3</v>
       </c>
     </row>
@@ -1290,7 +1317,7 @@
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D22">
         <v>2</v>
@@ -1302,19 +1329,19 @@
         <v>27</v>
       </c>
       <c r="G22" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H22" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I22" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J22">
         <v>9</v>
       </c>
       <c r="K22" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L22">
         <v>6</v>
@@ -1325,16 +1352,16 @@
       <c r="O22">
         <v>1</v>
       </c>
-      <c r="S22" t="s">
-        <v>62</v>
-      </c>
-      <c r="T22" t="s">
-        <v>63</v>
-      </c>
-      <c r="U22" t="s">
-        <v>36</v>
-      </c>
-      <c r="X22">
+      <c r="X22" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y22" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB22">
         <v>3</v>
       </c>
     </row>
@@ -1346,7 +1373,7 @@
         <v>1</v>
       </c>
       <c r="C23" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D23">
         <v>3</v>
@@ -1358,39 +1385,39 @@
         <v>18</v>
       </c>
       <c r="G23" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H23" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I23" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J23">
         <v>18</v>
       </c>
       <c r="K23" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L23">
         <v>6</v>
       </c>
       <c r="M23" t="s">
-        <v>29</v>
-      </c>
-      <c r="S23" t="s">
-        <v>43</v>
-      </c>
-      <c r="T23" t="s">
-        <v>46</v>
-      </c>
-      <c r="U23" t="s">
-        <v>33</v>
-      </c>
-      <c r="V23" t="s">
-        <v>33</v>
-      </c>
-      <c r="X23">
+        <v>33</v>
+      </c>
+      <c r="X23" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y23" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z23" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA23" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB23">
         <v>3</v>
       </c>
     </row>
@@ -1402,7 +1429,7 @@
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D24">
         <v>1</v>
@@ -1414,15 +1441,15 @@
         <v>3</v>
       </c>
       <c r="G24" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H24" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I24" t="s">
-        <v>66</v>
-      </c>
-      <c r="X24">
+        <v>70</v>
+      </c>
+      <c r="AB24">
         <v>3</v>
       </c>
     </row>
@@ -1434,7 +1461,7 @@
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D25">
         <v>1</v>
@@ -1446,15 +1473,15 @@
         <v>-40</v>
       </c>
       <c r="G25" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H25" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I25" t="s">
-        <v>40</v>
-      </c>
-      <c r="X25">
+        <v>44</v>
+      </c>
+      <c r="AB25">
         <v>4</v>
       </c>
     </row>
@@ -1466,7 +1493,7 @@
         <v>1</v>
       </c>
       <c r="C26" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D26">
         <v>1</v>
@@ -1478,13 +1505,13 @@
         <v>-20</v>
       </c>
       <c r="G26" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H26" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I26" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J26">
         <v>5</v>
@@ -1493,12 +1520,12 @@
         <v>7</v>
       </c>
       <c r="M26" t="s">
-        <v>67</v>
-      </c>
-      <c r="U26" t="s">
-        <v>36</v>
-      </c>
-      <c r="X26">
+        <v>71</v>
+      </c>
+      <c r="Z26" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB26">
         <v>4</v>
       </c>
     </row>
@@ -1510,7 +1537,7 @@
         <v>1</v>
       </c>
       <c r="C27" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D27">
         <v>2</v>
@@ -1522,13 +1549,13 @@
         <v>-25</v>
       </c>
       <c r="G27" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H27" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I27" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J27">
         <v>0</v>
@@ -1542,10 +1569,10 @@
       <c r="O27">
         <v>1</v>
       </c>
-      <c r="U27" t="s">
-        <v>36</v>
-      </c>
-      <c r="X27">
+      <c r="Z27" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB27">
         <v>4</v>
       </c>
     </row>
@@ -1557,7 +1584,7 @@
         <v>1</v>
       </c>
       <c r="C28" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D28">
         <v>3</v>
@@ -1569,13 +1596,13 @@
         <v>-25</v>
       </c>
       <c r="G28" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H28" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I28" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J28">
         <v>0</v>
@@ -1589,10 +1616,10 @@
       <c r="O28">
         <v>6</v>
       </c>
-      <c r="U28" t="s">
-        <v>33</v>
-      </c>
-      <c r="X28">
+      <c r="Z28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB28">
         <v>4</v>
       </c>
     </row>
@@ -1604,7 +1631,7 @@
         <v>1</v>
       </c>
       <c r="C29" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D29">
         <v>4</v>
@@ -1616,15 +1643,15 @@
         <v>-25</v>
       </c>
       <c r="G29" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H29" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I29" t="s">
-        <v>68</v>
-      </c>
-      <c r="X29">
+        <v>72</v>
+      </c>
+      <c r="AB29">
         <v>4</v>
       </c>
     </row>
@@ -1636,7 +1663,7 @@
         <v>1</v>
       </c>
       <c r="C30" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D30">
         <v>1</v>
@@ -1648,19 +1675,19 @@
         <v>-27</v>
       </c>
       <c r="G30" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H30" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I30" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J30">
         <v>0</v>
       </c>
       <c r="K30" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L30">
         <v>7</v>
@@ -1671,16 +1698,16 @@
       <c r="O30">
         <v>5</v>
       </c>
-      <c r="S30" t="s">
-        <v>43</v>
-      </c>
-      <c r="T30" t="s">
-        <v>69</v>
-      </c>
-      <c r="U30" t="s">
-        <v>33</v>
-      </c>
-      <c r="X30">
+      <c r="X30" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y30" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z30" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB30">
         <v>5</v>
       </c>
     </row>
@@ -1692,7 +1719,7 @@
         <v>1</v>
       </c>
       <c r="C31" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D31">
         <v>2</v>
@@ -1704,36 +1731,36 @@
         <v>-27</v>
       </c>
       <c r="G31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H31" t="s">
+        <v>34</v>
+      </c>
+      <c r="I31" t="s">
+        <v>35</v>
+      </c>
+      <c r="J31">
+        <v>6</v>
+      </c>
+      <c r="K31" t="s">
+        <v>49</v>
+      </c>
+      <c r="L31">
+        <v>6</v>
+      </c>
+      <c r="M31" t="s">
         <v>36</v>
       </c>
-      <c r="H31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31" t="s">
-        <v>31</v>
-      </c>
-      <c r="J31">
-        <v>6</v>
-      </c>
-      <c r="K31" t="s">
-        <v>45</v>
-      </c>
-      <c r="L31">
-        <v>6</v>
-      </c>
-      <c r="M31" t="s">
-        <v>32</v>
-      </c>
-      <c r="S31" t="s">
-        <v>54</v>
-      </c>
-      <c r="T31" t="s">
-        <v>55</v>
-      </c>
-      <c r="U31" t="s">
-        <v>33</v>
-      </c>
-      <c r="X31">
+      <c r="X31" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y31" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z31" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB31">
         <v>5</v>
       </c>
     </row>
@@ -1745,7 +1772,7 @@
         <v>1</v>
       </c>
       <c r="C32" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D32">
         <v>3</v>
@@ -1757,39 +1784,39 @@
         <v>-33</v>
       </c>
       <c r="G32" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H32" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I32" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J32">
         <v>67</v>
       </c>
       <c r="K32" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L32">
         <v>7</v>
       </c>
       <c r="M32" t="s">
-        <v>29</v>
-      </c>
-      <c r="S32" t="s">
-        <v>43</v>
-      </c>
-      <c r="T32" t="s">
-        <v>46</v>
-      </c>
-      <c r="U32" t="s">
-        <v>33</v>
-      </c>
-      <c r="V32" t="s">
-        <v>33</v>
-      </c>
-      <c r="X32">
+        <v>33</v>
+      </c>
+      <c r="X32" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y32" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z32" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA32" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB32">
         <v>5</v>
       </c>
     </row>
@@ -1801,7 +1828,7 @@
         <v>1</v>
       </c>
       <c r="C33" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D33">
         <v>1</v>
@@ -1813,15 +1840,15 @@
         <v>3</v>
       </c>
       <c r="G33" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H33" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I33" t="s">
-        <v>66</v>
-      </c>
-      <c r="X33">
+        <v>70</v>
+      </c>
+      <c r="AB33">
         <v>5</v>
       </c>
     </row>
@@ -1833,7 +1860,7 @@
         <v>1</v>
       </c>
       <c r="C34" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D34">
         <v>1</v>
@@ -1845,15 +1872,15 @@
         <v>-40</v>
       </c>
       <c r="G34" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H34" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I34" t="s">
-        <v>28</v>
-      </c>
-      <c r="X34">
+        <v>32</v>
+      </c>
+      <c r="AB34">
         <v>6</v>
       </c>
     </row>
@@ -1865,7 +1892,7 @@
         <v>1</v>
       </c>
       <c r="C35" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D35">
         <v>1</v>
@@ -1877,13 +1904,13 @@
         <v>-20</v>
       </c>
       <c r="G35" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H35" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I35" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J35">
         <v>4</v>
@@ -1891,10 +1918,10 @@
       <c r="L35">
         <v>6</v>
       </c>
-      <c r="U35" t="s">
-        <v>36</v>
-      </c>
-      <c r="X35">
+      <c r="Z35" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB35">
         <v>6</v>
       </c>
     </row>
@@ -1906,7 +1933,7 @@
         <v>1</v>
       </c>
       <c r="C36" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D36">
         <v>2</v>
@@ -1918,13 +1945,13 @@
         <v>-24</v>
       </c>
       <c r="G36" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H36" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I36" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J36">
         <v>5</v>
@@ -1933,12 +1960,12 @@
         <v>5</v>
       </c>
       <c r="M36" t="s">
-        <v>37</v>
-      </c>
-      <c r="U36" t="s">
-        <v>36</v>
-      </c>
-      <c r="X36">
+        <v>41</v>
+      </c>
+      <c r="Z36" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB36">
         <v>6</v>
       </c>
     </row>
@@ -1950,7 +1977,7 @@
         <v>2</v>
       </c>
       <c r="C37" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D37">
         <v>3</v>
@@ -1962,13 +1989,13 @@
         <v>-29</v>
       </c>
       <c r="G37" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H37" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I37" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J37">
         <v>0</v>
@@ -1982,10 +2009,10 @@
       <c r="O37">
         <v>6</v>
       </c>
-      <c r="U37" t="s">
-        <v>33</v>
-      </c>
-      <c r="X37">
+      <c r="Z37" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB37">
         <v>6</v>
       </c>
     </row>
@@ -1997,7 +2024,7 @@
         <v>2</v>
       </c>
       <c r="C38" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D38">
         <v>4</v>
@@ -2009,15 +2036,15 @@
         <v>-29</v>
       </c>
       <c r="G38" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H38" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I38" t="s">
-        <v>71</v>
-      </c>
-      <c r="X38">
+        <v>75</v>
+      </c>
+      <c r="AB38">
         <v>6</v>
       </c>
     </row>
@@ -2029,7 +2056,7 @@
         <v>2</v>
       </c>
       <c r="C39" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D39">
         <v>1</v>
@@ -2041,42 +2068,42 @@
         <v>-41</v>
       </c>
       <c r="G39" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H39" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I39" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J39">
         <v>6</v>
       </c>
       <c r="K39" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L39">
         <v>7</v>
       </c>
       <c r="M39" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q39">
+        <v>36</v>
+      </c>
+      <c r="V39">
         <v>0</v>
       </c>
-      <c r="S39" t="s">
-        <v>43</v>
-      </c>
-      <c r="T39" t="s">
-        <v>72</v>
-      </c>
-      <c r="U39" t="s">
-        <v>33</v>
-      </c>
-      <c r="V39" t="s">
-        <v>36</v>
-      </c>
-      <c r="X39">
+      <c r="X39" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y39" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z39" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB39">
         <v>7</v>
       </c>
     </row>
@@ -2088,7 +2115,7 @@
         <v>2</v>
       </c>
       <c r="C40" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D40">
         <v>2</v>
@@ -2100,19 +2127,19 @@
         <v>-47</v>
       </c>
       <c r="G40" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H40" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I40" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J40">
         <v>14</v>
       </c>
       <c r="K40" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L40">
         <v>6</v>
@@ -2123,16 +2150,16 @@
       <c r="O40">
         <v>3</v>
       </c>
-      <c r="S40" t="s">
-        <v>73</v>
-      </c>
-      <c r="T40" t="s">
-        <v>74</v>
-      </c>
-      <c r="U40" t="s">
-        <v>33</v>
-      </c>
-      <c r="X40">
+      <c r="X40" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y40" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z40" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB40">
         <v>7</v>
       </c>
     </row>
@@ -2144,7 +2171,7 @@
         <v>2</v>
       </c>
       <c r="C41" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D41">
         <v>1</v>
@@ -2156,19 +2183,19 @@
         <v>39</v>
       </c>
       <c r="G41" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H41" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I41" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J41">
         <v>39</v>
       </c>
       <c r="K41" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L41">
         <v>6</v>
@@ -2179,16 +2206,16 @@
       <c r="O41">
         <v>8</v>
       </c>
-      <c r="S41" t="s">
-        <v>62</v>
-      </c>
-      <c r="T41" t="s">
-        <v>76</v>
-      </c>
-      <c r="U41" t="s">
-        <v>33</v>
-      </c>
-      <c r="X41">
+      <c r="X41" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y41" t="s">
+        <v>80</v>
+      </c>
+      <c r="Z41" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB41">
         <v>7</v>
       </c>
     </row>
@@ -2200,7 +2227,7 @@
         <v>2</v>
       </c>
       <c r="C42" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D42">
         <v>1</v>
@@ -2212,15 +2239,15 @@
         <v>3</v>
       </c>
       <c r="G42" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H42" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I42" t="s">
-        <v>66</v>
-      </c>
-      <c r="X42">
+        <v>70</v>
+      </c>
+      <c r="AB42">
         <v>7</v>
       </c>
     </row>
@@ -2232,7 +2259,7 @@
         <v>2</v>
       </c>
       <c r="C43" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D43">
         <v>1</v>
@@ -2244,15 +2271,15 @@
         <v>-40</v>
       </c>
       <c r="G43" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H43" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I43" t="s">
-        <v>40</v>
-      </c>
-      <c r="X43">
+        <v>44</v>
+      </c>
+      <c r="AB43">
         <v>8</v>
       </c>
     </row>
@@ -2264,7 +2291,7 @@
         <v>2</v>
       </c>
       <c r="C44" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D44">
         <v>1</v>
@@ -2276,13 +2303,13 @@
         <v>-20</v>
       </c>
       <c r="G44" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H44" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I44" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J44">
         <v>11</v>
@@ -2296,10 +2323,10 @@
       <c r="O44">
         <v>6</v>
       </c>
-      <c r="U44" t="s">
-        <v>33</v>
-      </c>
-      <c r="X44">
+      <c r="Z44" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB44">
         <v>8</v>
       </c>
     </row>
@@ -2311,7 +2338,7 @@
         <v>2</v>
       </c>
       <c r="C45" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D45">
         <v>1</v>
@@ -2323,13 +2350,13 @@
         <v>-31</v>
       </c>
       <c r="G45" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H45" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I45" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J45">
         <v>-3</v>
@@ -2343,10 +2370,10 @@
       <c r="O45">
         <v>2</v>
       </c>
-      <c r="U45" t="s">
-        <v>36</v>
-      </c>
-      <c r="X45">
+      <c r="Z45" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB45">
         <v>8</v>
       </c>
     </row>
@@ -2358,7 +2385,7 @@
         <v>2</v>
       </c>
       <c r="C46" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D46">
         <v>2</v>
@@ -2370,13 +2397,13 @@
         <v>-28</v>
       </c>
       <c r="G46" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H46" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I46" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J46">
         <v>0</v>
@@ -2390,10 +2417,10 @@
       <c r="O46">
         <v>3</v>
       </c>
-      <c r="U46" t="s">
-        <v>33</v>
-      </c>
-      <c r="X46">
+      <c r="Z46" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB46">
         <v>8</v>
       </c>
     </row>
@@ -2405,7 +2432,7 @@
         <v>2</v>
       </c>
       <c r="C47" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D47">
         <v>3</v>
@@ -2417,13 +2444,13 @@
         <v>-28</v>
       </c>
       <c r="G47" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H47" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I47" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L47">
         <v>6</v>
@@ -2434,10 +2461,10 @@
       <c r="O47">
         <v>6</v>
       </c>
-      <c r="U47" t="s">
-        <v>33</v>
-      </c>
-      <c r="X47">
+      <c r="Z47" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB47">
         <v>8</v>
       </c>
     </row>
@@ -2449,7 +2476,7 @@
         <v>2</v>
       </c>
       <c r="C48" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D48">
         <v>1</v>
@@ -2461,15 +2488,15 @@
         <v>3</v>
       </c>
       <c r="G48" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H48" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I48" t="s">
-        <v>66</v>
-      </c>
-      <c r="X48">
+        <v>70</v>
+      </c>
+      <c r="AB48">
         <v>8</v>
       </c>
     </row>
@@ -2481,7 +2508,7 @@
         <v>2</v>
       </c>
       <c r="C49" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D49">
         <v>1</v>
@@ -2493,15 +2520,15 @@
         <v>-40</v>
       </c>
       <c r="G49" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H49" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I49" t="s">
-        <v>28</v>
-      </c>
-      <c r="X49">
+        <v>32</v>
+      </c>
+      <c r="AB49">
         <v>9</v>
       </c>
     </row>
@@ -2513,7 +2540,7 @@
         <v>2</v>
       </c>
       <c r="C50" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D50">
         <v>1</v>
@@ -2525,13 +2552,13 @@
         <v>-20</v>
       </c>
       <c r="G50" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H50" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I50" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J50">
         <v>-1</v>
@@ -2540,12 +2567,12 @@
         <v>5</v>
       </c>
       <c r="M50" t="s">
-        <v>51</v>
-      </c>
-      <c r="U50" t="s">
-        <v>36</v>
-      </c>
-      <c r="X50">
+        <v>55</v>
+      </c>
+      <c r="Z50" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB50">
         <v>9</v>
       </c>
     </row>
@@ -2557,7 +2584,7 @@
         <v>2</v>
       </c>
       <c r="C51" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D51">
         <v>2</v>
@@ -2569,13 +2596,13 @@
         <v>-19</v>
       </c>
       <c r="G51" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H51" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I51" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J51">
         <v>0</v>
@@ -2589,10 +2616,10 @@
       <c r="O51">
         <v>5</v>
       </c>
-      <c r="U51" t="s">
-        <v>36</v>
-      </c>
-      <c r="X51">
+      <c r="Z51" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB51">
         <v>9</v>
       </c>
     </row>
@@ -2604,7 +2631,7 @@
         <v>2</v>
       </c>
       <c r="C52" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D52">
         <v>3</v>
@@ -2616,13 +2643,13 @@
         <v>-19</v>
       </c>
       <c r="G52" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H52" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I52" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="J52">
         <v>1</v>
@@ -2630,10 +2657,10 @@
       <c r="L52">
         <v>5</v>
       </c>
-      <c r="U52" t="s">
-        <v>33</v>
-      </c>
-      <c r="X52">
+      <c r="Z52" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB52">
         <v>9</v>
       </c>
     </row>
@@ -2645,7 +2672,7 @@
         <v>2</v>
       </c>
       <c r="C53" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D53">
         <v>4</v>
@@ -2657,15 +2684,15 @@
         <v>-20</v>
       </c>
       <c r="G53" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H53" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I53" t="s">
-        <v>68</v>
-      </c>
-      <c r="X53">
+        <v>72</v>
+      </c>
+      <c r="AB53">
         <v>9</v>
       </c>
     </row>
@@ -2677,7 +2704,7 @@
         <v>2</v>
       </c>
       <c r="C54" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D54">
         <v>1</v>
@@ -2689,19 +2716,19 @@
         <v>39</v>
       </c>
       <c r="G54" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H54" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I54" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J54">
         <v>13</v>
       </c>
       <c r="K54" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L54">
         <v>6</v>
@@ -2712,16 +2739,16 @@
       <c r="O54">
         <v>5</v>
       </c>
-      <c r="S54" t="s">
-        <v>62</v>
-      </c>
-      <c r="T54" t="s">
-        <v>52</v>
-      </c>
-      <c r="U54" t="s">
-        <v>33</v>
-      </c>
-      <c r="X54">
+      <c r="X54" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y54" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z54" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB54">
         <v>10</v>
       </c>
     </row>
@@ -2733,7 +2760,7 @@
         <v>2</v>
       </c>
       <c r="C55" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D55">
         <v>1</v>
@@ -2745,39 +2772,39 @@
         <v>26</v>
       </c>
       <c r="G55" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H55" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I55" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J55">
         <v>12</v>
       </c>
       <c r="K55" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L55">
         <v>6</v>
       </c>
       <c r="M55" t="s">
-        <v>32</v>
-      </c>
-      <c r="S55" t="s">
-        <v>43</v>
-      </c>
-      <c r="T55" t="s">
-        <v>72</v>
-      </c>
-      <c r="U55" t="s">
-        <v>33</v>
-      </c>
-      <c r="V55" t="s">
         <v>36</v>
       </c>
-      <c r="X55">
+      <c r="X55" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y55" t="s">
+        <v>76</v>
+      </c>
+      <c r="Z55" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA55" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB55">
         <v>10</v>
       </c>
     </row>
@@ -2789,7 +2816,7 @@
         <v>2</v>
       </c>
       <c r="C56" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D56">
         <v>1</v>
@@ -2801,36 +2828,36 @@
         <v>14</v>
       </c>
       <c r="G56" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H56" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I56" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J56">
         <v>9</v>
       </c>
       <c r="K56" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L56">
         <v>6</v>
       </c>
       <c r="M56" t="s">
-        <v>32</v>
-      </c>
-      <c r="S56" t="s">
-        <v>73</v>
-      </c>
-      <c r="T56" t="s">
-        <v>78</v>
-      </c>
-      <c r="U56" t="s">
         <v>36</v>
       </c>
-      <c r="X56">
+      <c r="X56" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y56" t="s">
+        <v>82</v>
+      </c>
+      <c r="Z56" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB56">
         <v>10</v>
       </c>
     </row>
@@ -2842,7 +2869,7 @@
         <v>2</v>
       </c>
       <c r="C57" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D57">
         <v>2</v>
@@ -2854,36 +2881,36 @@
         <v>5</v>
       </c>
       <c r="G57" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H57" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I57" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J57">
         <v>4</v>
       </c>
       <c r="K57" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L57">
         <v>6</v>
       </c>
       <c r="M57" t="s">
-        <v>29</v>
-      </c>
-      <c r="S57" t="s">
-        <v>47</v>
-      </c>
-      <c r="T57" t="s">
-        <v>46</v>
-      </c>
-      <c r="U57" t="s">
-        <v>33</v>
-      </c>
-      <c r="X57">
+        <v>33</v>
+      </c>
+      <c r="X57" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y57" t="s">
+        <v>50</v>
+      </c>
+      <c r="Z57" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB57">
         <v>10</v>
       </c>
     </row>
@@ -2895,7 +2922,7 @@
         <v>2</v>
       </c>
       <c r="C58" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D58">
         <v>1</v>
@@ -2907,36 +2934,36 @@
         <v>1</v>
       </c>
       <c r="G58" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H58" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I58" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J58">
         <v>1</v>
       </c>
       <c r="K58" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L58">
         <v>9</v>
       </c>
       <c r="M58" t="s">
-        <v>32</v>
-      </c>
-      <c r="S58" t="s">
-        <v>79</v>
-      </c>
-      <c r="T58" t="s">
-        <v>69</v>
-      </c>
-      <c r="U58" t="s">
-        <v>33</v>
-      </c>
-      <c r="X58">
+        <v>36</v>
+      </c>
+      <c r="X58" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y58" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z58" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB58">
         <v>10</v>
       </c>
     </row>
@@ -2948,7 +2975,7 @@
         <v>2</v>
       </c>
       <c r="C59" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D59">
         <v>1</v>
@@ -2960,15 +2987,15 @@
         <v>3</v>
       </c>
       <c r="G59" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H59" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I59" t="s">
-        <v>66</v>
-      </c>
-      <c r="X59">
+        <v>70</v>
+      </c>
+      <c r="AB59">
         <v>10</v>
       </c>
     </row>
@@ -2980,7 +3007,7 @@
         <v>2</v>
       </c>
       <c r="C60" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D60">
         <v>1</v>
@@ -2992,15 +3019,15 @@
         <v>-40</v>
       </c>
       <c r="G60" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H60" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I60" t="s">
-        <v>40</v>
-      </c>
-      <c r="X60">
+        <v>44</v>
+      </c>
+      <c r="AB60">
         <v>11</v>
       </c>
     </row>
@@ -3012,7 +3039,7 @@
         <v>2</v>
       </c>
       <c r="C61" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D61">
         <v>1</v>
@@ -3024,13 +3051,13 @@
         <v>-13</v>
       </c>
       <c r="G61" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H61" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I61" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J61">
         <v>7</v>
@@ -3039,12 +3066,12 @@
         <v>5</v>
       </c>
       <c r="M61" t="s">
-        <v>51</v>
-      </c>
-      <c r="U61" t="s">
-        <v>33</v>
-      </c>
-      <c r="X61">
+        <v>55</v>
+      </c>
+      <c r="Z61" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB61">
         <v>11</v>
       </c>
     </row>
@@ -3056,7 +3083,7 @@
         <v>2</v>
       </c>
       <c r="C62" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D62">
         <v>2</v>
@@ -3068,13 +3095,13 @@
         <v>-20</v>
       </c>
       <c r="G62" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H62" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I62" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J62">
         <v>-2</v>
@@ -3083,12 +3110,12 @@
         <v>5</v>
       </c>
       <c r="M62" t="s">
-        <v>32</v>
-      </c>
-      <c r="U62" t="s">
-        <v>33</v>
-      </c>
-      <c r="X62">
+        <v>36</v>
+      </c>
+      <c r="Z62" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB62">
         <v>11</v>
       </c>
     </row>
@@ -3100,7 +3127,7 @@
         <v>2</v>
       </c>
       <c r="C63" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D63">
         <v>3</v>
@@ -3112,13 +3139,13 @@
         <v>-18</v>
       </c>
       <c r="G63" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H63" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I63" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="L63">
         <v>6</v>
@@ -3129,10 +3156,10 @@
       <c r="O63">
         <v>1</v>
       </c>
-      <c r="U63" t="s">
-        <v>36</v>
-      </c>
-      <c r="X63">
+      <c r="Z63" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB63">
         <v>11</v>
       </c>
     </row>
@@ -3144,7 +3171,7 @@
         <v>2</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D64">
         <v>1</v>
@@ -3156,15 +3183,15 @@
         <v>3</v>
       </c>
       <c r="G64" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H64" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I64" t="s">
-        <v>66</v>
-      </c>
-      <c r="X64">
+        <v>70</v>
+      </c>
+      <c r="AB64">
         <v>11</v>
       </c>
     </row>
@@ -3176,7 +3203,7 @@
         <v>2</v>
       </c>
       <c r="C65" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D65">
         <v>1</v>
@@ -3188,15 +3215,15 @@
         <v>-40</v>
       </c>
       <c r="G65" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H65" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I65" t="s">
-        <v>40</v>
-      </c>
-      <c r="X65">
+        <v>44</v>
+      </c>
+      <c r="AB65">
         <v>12</v>
       </c>
     </row>
@@ -3208,7 +3235,7 @@
         <v>2</v>
       </c>
       <c r="C66" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D66">
         <v>1</v>
@@ -3220,13 +3247,13 @@
         <v>-25</v>
       </c>
       <c r="G66" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H66" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I66" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J66">
         <v>11</v>
@@ -3240,10 +3267,10 @@
       <c r="O66">
         <v>2</v>
       </c>
-      <c r="U66" t="s">
-        <v>33</v>
-      </c>
-      <c r="X66">
+      <c r="Z66" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB66">
         <v>12</v>
       </c>
     </row>
@@ -3255,7 +3282,7 @@
         <v>2</v>
       </c>
       <c r="C67" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D67">
         <v>1</v>
@@ -3267,13 +3294,13 @@
         <v>-36</v>
       </c>
       <c r="G67" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H67" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I67" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J67">
         <v>3</v>
@@ -3282,12 +3309,12 @@
         <v>7</v>
       </c>
       <c r="M67" t="s">
-        <v>51</v>
-      </c>
-      <c r="U67" t="s">
-        <v>36</v>
-      </c>
-      <c r="X67">
+        <v>55</v>
+      </c>
+      <c r="Z67" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB67">
         <v>12</v>
       </c>
     </row>
@@ -3299,7 +3326,7 @@
         <v>2</v>
       </c>
       <c r="C68" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D68">
         <v>2</v>
@@ -3311,13 +3338,13 @@
         <v>-39</v>
       </c>
       <c r="G68" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H68" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I68" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="L68">
         <v>6</v>
@@ -3328,10 +3355,10 @@
       <c r="O68">
         <v>2</v>
       </c>
-      <c r="U68" t="s">
-        <v>36</v>
-      </c>
-      <c r="X68">
+      <c r="Z68" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB68">
         <v>12</v>
       </c>
     </row>
@@ -3343,7 +3370,7 @@
         <v>2</v>
       </c>
       <c r="C69" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D69">
         <v>1</v>
@@ -3355,15 +3382,15 @@
         <v>3</v>
       </c>
       <c r="G69" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H69" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I69" t="s">
-        <v>66</v>
-      </c>
-      <c r="X69">
+        <v>70</v>
+      </c>
+      <c r="AB69">
         <v>12</v>
       </c>
     </row>
@@ -3375,7 +3402,7 @@
         <v>2</v>
       </c>
       <c r="C70" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D70">
         <v>1</v>
@@ -3387,15 +3414,15 @@
         <v>-40</v>
       </c>
       <c r="G70" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H70" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I70" t="s">
-        <v>40</v>
-      </c>
-      <c r="X70">
+        <v>44</v>
+      </c>
+      <c r="AB70">
         <v>13</v>
       </c>
     </row>
@@ -3407,7 +3434,7 @@
         <v>2</v>
       </c>
       <c r="C71" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D71">
         <v>1</v>
@@ -3419,13 +3446,13 @@
         <v>-35</v>
       </c>
       <c r="G71" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H71" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I71" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J71">
         <v>2</v>
@@ -3434,12 +3461,12 @@
         <v>6</v>
       </c>
       <c r="M71" t="s">
-        <v>32</v>
-      </c>
-      <c r="U71" t="s">
-        <v>33</v>
-      </c>
-      <c r="X71">
+        <v>36</v>
+      </c>
+      <c r="Z71" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB71">
         <v>13</v>
       </c>
     </row>
@@ -3451,7 +3478,7 @@
         <v>2</v>
       </c>
       <c r="C72" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D72">
         <v>2</v>
@@ -3463,13 +3490,13 @@
         <v>-37</v>
       </c>
       <c r="G72" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H72" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I72" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J72">
         <v>0</v>
@@ -3483,10 +3510,10 @@
       <c r="O72">
         <v>9</v>
       </c>
-      <c r="U72" t="s">
-        <v>33</v>
-      </c>
-      <c r="X72">
+      <c r="Z72" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB72">
         <v>13</v>
       </c>
     </row>
@@ -3498,7 +3525,7 @@
         <v>2</v>
       </c>
       <c r="C73" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D73">
         <v>3</v>
@@ -3510,13 +3537,13 @@
         <v>-37</v>
       </c>
       <c r="G73" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H73" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I73" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J73">
         <v>3</v>
@@ -3525,12 +3552,12 @@
         <v>5</v>
       </c>
       <c r="M73" t="s">
-        <v>51</v>
-      </c>
-      <c r="U73" t="s">
-        <v>33</v>
-      </c>
-      <c r="X73">
+        <v>55</v>
+      </c>
+      <c r="Z73" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB73">
         <v>13</v>
       </c>
     </row>
@@ -3542,7 +3569,7 @@
         <v>3</v>
       </c>
       <c r="C74" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D74">
         <v>1</v>
@@ -3554,15 +3581,15 @@
         <v>-40</v>
       </c>
       <c r="G74" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H74" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="I74" t="s">
-        <v>40</v>
-      </c>
-      <c r="X74">
+        <v>44</v>
+      </c>
+      <c r="AB74">
         <v>13</v>
       </c>
     </row>
@@ -3574,7 +3601,7 @@
         <v>3</v>
       </c>
       <c r="C75" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D75">
         <v>1</v>
@@ -3586,19 +3613,19 @@
         <v>-25</v>
       </c>
       <c r="G75" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H75" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I75" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J75">
         <v>0</v>
       </c>
       <c r="K75" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L75">
         <v>6</v>
@@ -3609,16 +3636,16 @@
       <c r="O75">
         <v>2</v>
       </c>
-      <c r="S75" t="s">
-        <v>58</v>
-      </c>
-      <c r="T75" t="s">
-        <v>59</v>
-      </c>
-      <c r="U75" t="s">
-        <v>36</v>
-      </c>
-      <c r="X75">
+      <c r="X75" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y75" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z75" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB75">
         <v>13</v>
       </c>
     </row>
@@ -3630,7 +3657,7 @@
         <v>3</v>
       </c>
       <c r="C76" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D76">
         <v>2</v>
@@ -3642,36 +3669,36 @@
         <v>-25</v>
       </c>
       <c r="G76" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H76" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I76" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J76">
         <v>20</v>
       </c>
       <c r="K76" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L76">
         <v>6</v>
       </c>
       <c r="M76" t="s">
-        <v>67</v>
-      </c>
-      <c r="S76" t="s">
-        <v>58</v>
-      </c>
-      <c r="T76" t="s">
-        <v>82</v>
-      </c>
-      <c r="U76" t="s">
-        <v>33</v>
-      </c>
-      <c r="X76">
+        <v>71</v>
+      </c>
+      <c r="X76" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y76" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z76" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB76">
         <v>13</v>
       </c>
     </row>
@@ -3683,7 +3710,7 @@
         <v>3</v>
       </c>
       <c r="C77" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D77">
         <v>1</v>
@@ -3695,19 +3722,19 @@
         <v>-45</v>
       </c>
       <c r="G77" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H77" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I77" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J77">
         <v>4</v>
       </c>
       <c r="K77" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L77">
         <v>8</v>
@@ -3718,16 +3745,16 @@
       <c r="O77">
         <v>1</v>
       </c>
-      <c r="S77" t="s">
-        <v>43</v>
-      </c>
-      <c r="T77" t="s">
-        <v>83</v>
-      </c>
-      <c r="U77" t="s">
-        <v>36</v>
-      </c>
-      <c r="X77">
+      <c r="X77" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y77" t="s">
+        <v>87</v>
+      </c>
+      <c r="Z77" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB77">
         <v>13</v>
       </c>
     </row>
@@ -3739,7 +3766,7 @@
         <v>3</v>
       </c>
       <c r="C78" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D78">
         <v>2</v>
@@ -3751,19 +3778,19 @@
         <v>-49</v>
       </c>
       <c r="G78" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H78" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I78" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J78">
         <v>8</v>
       </c>
       <c r="K78" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L78">
         <v>6</v>
@@ -3774,16 +3801,16 @@
       <c r="O78">
         <v>1</v>
       </c>
-      <c r="S78" t="s">
-        <v>58</v>
-      </c>
-      <c r="T78" t="s">
-        <v>82</v>
-      </c>
-      <c r="U78" t="s">
-        <v>36</v>
-      </c>
-      <c r="X78">
+      <c r="X78" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y78" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z78" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB78">
         <v>13</v>
       </c>
     </row>
@@ -3795,7 +3822,7 @@
         <v>3</v>
       </c>
       <c r="C79" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D79">
         <v>1</v>
@@ -3807,36 +3834,36 @@
         <v>43</v>
       </c>
       <c r="G79" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H79" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I79" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J79">
         <v>2</v>
       </c>
       <c r="K79" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L79">
         <v>7</v>
       </c>
       <c r="M79" t="s">
-        <v>51</v>
-      </c>
-      <c r="S79" t="s">
-        <v>54</v>
-      </c>
-      <c r="T79" t="s">
         <v>55</v>
       </c>
-      <c r="U79" t="s">
-        <v>36</v>
-      </c>
-      <c r="X79">
+      <c r="X79" t="s">
+        <v>58</v>
+      </c>
+      <c r="Y79" t="s">
+        <v>59</v>
+      </c>
+      <c r="Z79" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB79">
         <v>13</v>
       </c>
     </row>
@@ -3848,7 +3875,7 @@
         <v>3</v>
       </c>
       <c r="C80" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D80">
         <v>2</v>
@@ -3860,19 +3887,19 @@
         <v>41</v>
       </c>
       <c r="G80" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H80" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I80" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J80">
         <v>0</v>
       </c>
       <c r="K80" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L80">
         <v>7</v>
@@ -3883,16 +3910,16 @@
       <c r="O80">
         <v>6</v>
       </c>
-      <c r="S80" t="s">
-        <v>43</v>
-      </c>
-      <c r="T80" t="s">
-        <v>84</v>
-      </c>
-      <c r="U80" t="s">
-        <v>33</v>
-      </c>
-      <c r="X80">
+      <c r="X80" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y80" t="s">
+        <v>88</v>
+      </c>
+      <c r="Z80" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB80">
         <v>13</v>
       </c>
     </row>
@@ -3904,7 +3931,7 @@
         <v>3</v>
       </c>
       <c r="C81" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D81">
         <v>3</v>
@@ -3916,19 +3943,19 @@
         <v>41</v>
       </c>
       <c r="G81" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H81" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I81" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J81">
         <v>11</v>
       </c>
       <c r="K81" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L81">
         <v>6</v>
@@ -3939,16 +3966,16 @@
       <c r="O81">
         <v>3</v>
       </c>
-      <c r="S81" t="s">
-        <v>58</v>
-      </c>
-      <c r="T81" t="s">
-        <v>85</v>
-      </c>
-      <c r="U81" t="s">
-        <v>33</v>
-      </c>
-      <c r="X81">
+      <c r="X81" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y81" t="s">
+        <v>89</v>
+      </c>
+      <c r="Z81" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB81">
         <v>13</v>
       </c>
     </row>
@@ -3960,7 +3987,7 @@
         <v>3</v>
       </c>
       <c r="C82" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D82">
         <v>1</v>
@@ -3972,19 +3999,19 @@
         <v>30</v>
       </c>
       <c r="G82" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H82" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I82" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J82">
         <v>0</v>
       </c>
       <c r="K82" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L82">
         <v>5</v>
@@ -3995,16 +4022,16 @@
       <c r="O82">
         <v>7</v>
       </c>
-      <c r="S82" t="s">
-        <v>58</v>
-      </c>
-      <c r="T82" t="s">
-        <v>59</v>
-      </c>
-      <c r="U82" t="s">
-        <v>36</v>
-      </c>
-      <c r="X82">
+      <c r="X82" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y82" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z82" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB82">
         <v>9</v>
       </c>
     </row>
@@ -4016,7 +4043,7 @@
         <v>3</v>
       </c>
       <c r="C83" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D83">
         <v>2</v>
@@ -4028,27 +4055,27 @@
         <v>30</v>
       </c>
       <c r="G83" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H83" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I83" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J83">
         <v>-8</v>
       </c>
-      <c r="S83" t="s">
-        <v>58</v>
-      </c>
-      <c r="T83" t="s">
-        <v>82</v>
-      </c>
-      <c r="U83" t="s">
-        <v>36</v>
-      </c>
-      <c r="X83">
+      <c r="X83" t="s">
+        <v>62</v>
+      </c>
+      <c r="Y83" t="s">
+        <v>86</v>
+      </c>
+      <c r="Z83" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB83">
         <v>9</v>
       </c>
     </row>
@@ -4060,7 +4087,7 @@
         <v>3</v>
       </c>
       <c r="C84" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D84">
         <v>2</v>
@@ -4072,19 +4099,19 @@
         <v>38</v>
       </c>
       <c r="G84" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H84" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I84" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J84">
         <v>8</v>
       </c>
       <c r="K84" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L84">
         <v>6</v>
@@ -4095,16 +4122,16 @@
       <c r="O84">
         <v>3</v>
       </c>
-      <c r="S84" t="s">
-        <v>62</v>
-      </c>
-      <c r="T84" t="s">
-        <v>86</v>
-      </c>
-      <c r="U84" t="s">
-        <v>33</v>
-      </c>
-      <c r="X84">
+      <c r="X84" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y84" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z84" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB84">
         <v>9</v>
       </c>
     </row>
@@ -4116,7 +4143,7 @@
         <v>3</v>
       </c>
       <c r="C85" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D85">
         <v>3</v>
@@ -4128,36 +4155,36 @@
         <v>30</v>
       </c>
       <c r="G85" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H85" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I85" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J85">
         <v>1</v>
       </c>
       <c r="K85" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L85">
         <v>7</v>
       </c>
       <c r="M85" t="s">
-        <v>32</v>
-      </c>
-      <c r="S85" t="s">
-        <v>43</v>
-      </c>
-      <c r="T85" t="s">
-        <v>52</v>
-      </c>
-      <c r="U85" t="s">
         <v>36</v>
       </c>
-      <c r="X85">
+      <c r="X85" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y85" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z85" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB85">
         <v>9</v>
       </c>
     </row>
@@ -4169,7 +4196,7 @@
         <v>3</v>
       </c>
       <c r="C86" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D86">
         <v>4</v>
@@ -4181,19 +4208,19 @@
         <v>29</v>
       </c>
       <c r="G86" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H86" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I86" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J86">
         <v>29</v>
       </c>
       <c r="K86" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L86">
         <v>7</v>
@@ -4204,16 +4231,16 @@
       <c r="O86">
         <v>7</v>
       </c>
-      <c r="S86" t="s">
-        <v>62</v>
-      </c>
-      <c r="T86" t="s">
-        <v>86</v>
-      </c>
-      <c r="U86" t="s">
-        <v>36</v>
-      </c>
-      <c r="X86">
+      <c r="X86" t="s">
+        <v>66</v>
+      </c>
+      <c r="Y86" t="s">
+        <v>90</v>
+      </c>
+      <c r="Z86" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB86">
         <v>9</v>
       </c>
     </row>
@@ -4225,7 +4252,7 @@
         <v>3</v>
       </c>
       <c r="C87" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D87">
         <v>1</v>
@@ -4237,15 +4264,15 @@
         <v>3</v>
       </c>
       <c r="G87" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H87" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="I87" t="s">
-        <v>87</v>
-      </c>
-      <c r="X87">
+        <v>91</v>
+      </c>
+      <c r="AB87">
         <v>9</v>
       </c>
     </row>
@@ -4257,7 +4284,7 @@
         <v>3</v>
       </c>
       <c r="C88" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D88">
         <v>1</v>
@@ -4269,15 +4296,15 @@
         <v>-40</v>
       </c>
       <c r="G88" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H88" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="I88" t="s">
-        <v>40</v>
-      </c>
-      <c r="X88">
+        <v>44</v>
+      </c>
+      <c r="AB88">
         <v>10</v>
       </c>
     </row>
@@ -4289,7 +4316,7 @@
         <v>3</v>
       </c>
       <c r="C89" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D89">
         <v>1</v>
@@ -4301,13 +4328,13 @@
         <v>-24</v>
       </c>
       <c r="G89" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H89" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I89" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J89">
         <v>8</v>
@@ -4316,12 +4343,12 @@
         <v>6</v>
       </c>
       <c r="M89" t="s">
-        <v>37</v>
-      </c>
-      <c r="U89" t="s">
-        <v>33</v>
-      </c>
-      <c r="X89">
+        <v>41</v>
+      </c>
+      <c r="Z89" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB89">
         <v>10</v>
       </c>
     </row>
@@ -4333,7 +4360,7 @@
         <v>3</v>
       </c>
       <c r="C90" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D90">
         <v>2</v>
@@ -4345,13 +4372,13 @@
         <v>-32</v>
       </c>
       <c r="G90" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H90" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I90" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J90">
         <v>6</v>
@@ -4360,12 +4387,12 @@
         <v>5</v>
       </c>
       <c r="M90" t="s">
-        <v>32</v>
-      </c>
-      <c r="U90" t="s">
         <v>36</v>
       </c>
-      <c r="X90">
+      <c r="Z90" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB90">
         <v>10</v>
       </c>
     </row>
@@ -4377,7 +4404,7 @@
         <v>3</v>
       </c>
       <c r="C91" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D91">
         <v>1</v>
@@ -4389,13 +4416,13 @@
         <v>-38</v>
       </c>
       <c r="G91" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H91" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I91" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J91">
         <v>4</v>
@@ -4404,12 +4431,12 @@
         <v>5</v>
       </c>
       <c r="M91" t="s">
-        <v>51</v>
-      </c>
-      <c r="U91" t="s">
-        <v>33</v>
-      </c>
-      <c r="X91">
+        <v>55</v>
+      </c>
+      <c r="Z91" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB91">
         <v>10</v>
       </c>
     </row>
@@ -4421,7 +4448,7 @@
         <v>3</v>
       </c>
       <c r="C92" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D92">
         <v>2</v>
@@ -4433,13 +4460,13 @@
         <v>-42</v>
       </c>
       <c r="G92" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H92" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I92" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J92">
         <v>4</v>
@@ -4448,12 +4475,12 @@
         <v>5</v>
       </c>
       <c r="M92" t="s">
-        <v>37</v>
-      </c>
-      <c r="U92" t="s">
-        <v>33</v>
-      </c>
-      <c r="X92">
+        <v>41</v>
+      </c>
+      <c r="Z92" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB92">
         <v>10</v>
       </c>
     </row>
@@ -4465,7 +4492,7 @@
         <v>3</v>
       </c>
       <c r="C93" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D93">
         <v>3</v>
@@ -4477,13 +4504,13 @@
         <v>-46</v>
       </c>
       <c r="G93" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H93" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I93" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J93">
         <v>6</v>
@@ -4492,12 +4519,12 @@
         <v>5</v>
       </c>
       <c r="M93" t="s">
-        <v>32</v>
-      </c>
-      <c r="U93" t="s">
-        <v>33</v>
-      </c>
-      <c r="X93">
+        <v>36</v>
+      </c>
+      <c r="Z93" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB93">
         <v>10</v>
       </c>
     </row>
@@ -4509,7 +4536,7 @@
         <v>3</v>
       </c>
       <c r="C94" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D94">
         <v>1</v>
@@ -4521,13 +4548,13 @@
         <v>48</v>
       </c>
       <c r="G94" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H94" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I94" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J94">
         <v>5</v>
@@ -4536,12 +4563,12 @@
         <v>5</v>
       </c>
       <c r="M94" t="s">
-        <v>51</v>
-      </c>
-      <c r="U94" t="s">
-        <v>36</v>
-      </c>
-      <c r="X94">
+        <v>55</v>
+      </c>
+      <c r="Z94" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB94">
         <v>10</v>
       </c>
     </row>
@@ -4553,7 +4580,7 @@
         <v>3</v>
       </c>
       <c r="C95" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D95">
         <v>2</v>
@@ -4565,13 +4592,13 @@
         <v>43</v>
       </c>
       <c r="G95" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H95" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I95" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J95">
         <v>0</v>
@@ -4585,10 +4612,10 @@
       <c r="O95">
         <v>3</v>
       </c>
-      <c r="U95" t="s">
-        <v>33</v>
-      </c>
-      <c r="X95">
+      <c r="Z95" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB95">
         <v>10</v>
       </c>
     </row>
@@ -4600,7 +4627,7 @@
         <v>4</v>
       </c>
       <c r="C96" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D96">
         <v>3</v>
@@ -4612,13 +4639,13 @@
         <v>43</v>
       </c>
       <c r="G96" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H96" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I96" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J96">
         <v>2</v>
@@ -4627,12 +4654,12 @@
         <v>5</v>
       </c>
       <c r="M96" t="s">
-        <v>37</v>
-      </c>
-      <c r="U96" t="s">
-        <v>36</v>
-      </c>
-      <c r="X96">
+        <v>41</v>
+      </c>
+      <c r="Z96" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB96">
         <v>10</v>
       </c>
     </row>
@@ -4644,7 +4671,7 @@
         <v>4</v>
       </c>
       <c r="C97" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D97">
         <v>4</v>
@@ -4656,13 +4683,13 @@
         <v>41</v>
       </c>
       <c r="G97" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H97" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I97" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J97">
         <v>3</v>
@@ -4671,12 +4698,12 @@
         <v>6</v>
       </c>
       <c r="M97" t="s">
-        <v>51</v>
-      </c>
-      <c r="U97" t="s">
-        <v>33</v>
-      </c>
-      <c r="X97">
+        <v>55</v>
+      </c>
+      <c r="Z97" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB97">
         <v>10</v>
       </c>
     </row>
@@ -4688,7 +4715,7 @@
         <v>4</v>
       </c>
       <c r="C98" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D98">
         <v>1</v>
@@ -4700,13 +4727,13 @@
         <v>38</v>
       </c>
       <c r="G98" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H98" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I98" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J98">
         <v>12</v>
@@ -4715,12 +4742,12 @@
         <v>6</v>
       </c>
       <c r="M98" t="s">
-        <v>32</v>
-      </c>
-      <c r="U98" t="s">
-        <v>33</v>
-      </c>
-      <c r="X98">
+        <v>36</v>
+      </c>
+      <c r="Z98" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB98">
         <v>10</v>
       </c>
     </row>
@@ -4732,7 +4759,7 @@
         <v>4</v>
       </c>
       <c r="C99" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D99">
         <v>2</v>
@@ -4744,13 +4771,13 @@
         <v>36</v>
       </c>
       <c r="G99" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H99" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I99" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J99">
         <v>0</v>
@@ -4764,10 +4791,10 @@
       <c r="O99">
         <v>9</v>
       </c>
-      <c r="U99" t="s">
-        <v>33</v>
-      </c>
-      <c r="X99">
+      <c r="Z99" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB99">
         <v>10</v>
       </c>
     </row>
@@ -4779,7 +4806,7 @@
         <v>4</v>
       </c>
       <c r="C100" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D100">
         <v>3</v>
@@ -4791,13 +4818,13 @@
         <v>36</v>
       </c>
       <c r="G100" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H100" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I100" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J100">
         <v>7</v>
@@ -4806,12 +4833,12 @@
         <v>6</v>
       </c>
       <c r="M100" t="s">
-        <v>32</v>
-      </c>
-      <c r="U100" t="s">
         <v>36</v>
       </c>
-      <c r="X100">
+      <c r="Z100" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB100">
         <v>10</v>
       </c>
     </row>
@@ -4823,7 +4850,7 @@
         <v>4</v>
       </c>
       <c r="C101" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D101">
         <v>4</v>
@@ -4835,13 +4862,13 @@
         <v>29</v>
       </c>
       <c r="G101" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H101" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I101" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J101">
         <v>7</v>
@@ -4850,12 +4877,12 @@
         <v>6</v>
       </c>
       <c r="M101" t="s">
-        <v>32</v>
-      </c>
-      <c r="U101" t="s">
         <v>36</v>
       </c>
-      <c r="X101">
+      <c r="Z101" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB101">
         <v>10</v>
       </c>
     </row>
@@ -4867,7 +4894,7 @@
         <v>4</v>
       </c>
       <c r="C102" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D102">
         <v>3</v>
@@ -4879,13 +4906,13 @@
         <v>22</v>
       </c>
       <c r="G102" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H102" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I102" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J102">
         <v>2</v>
@@ -4894,12 +4921,12 @@
         <v>5</v>
       </c>
       <c r="M102" t="s">
-        <v>51</v>
-      </c>
-      <c r="U102" t="s">
-        <v>33</v>
-      </c>
-      <c r="X102">
+        <v>55</v>
+      </c>
+      <c r="Z102" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB102">
         <v>10</v>
       </c>
     </row>
@@ -4911,7 +4938,7 @@
         <v>4</v>
       </c>
       <c r="C103" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D103">
         <v>4</v>
@@ -4923,13 +4950,13 @@
         <v>20</v>
       </c>
       <c r="G103" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H103" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I103" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J103">
         <v>2</v>
@@ -4938,12 +4965,12 @@
         <v>5</v>
       </c>
       <c r="M103" t="s">
-        <v>32</v>
-      </c>
-      <c r="U103" t="s">
         <v>36</v>
       </c>
-      <c r="X103">
+      <c r="Z103" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB103">
         <v>10</v>
       </c>
     </row>
@@ -4955,7 +4982,7 @@
         <v>4</v>
       </c>
       <c r="C104" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D104">
         <v>1</v>
@@ -4967,13 +4994,13 @@
         <v>-18</v>
       </c>
       <c r="G104" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H104" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I104" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J104">
         <v>-1</v>
@@ -4982,12 +5009,12 @@
         <v>6</v>
       </c>
       <c r="M104" t="s">
-        <v>51</v>
-      </c>
-      <c r="U104" t="s">
-        <v>33</v>
-      </c>
-      <c r="X104">
+        <v>55</v>
+      </c>
+      <c r="Z104" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB104">
         <v>11</v>
       </c>
     </row>
@@ -4999,7 +5026,7 @@
         <v>4</v>
       </c>
       <c r="C105" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D105">
         <v>2</v>
@@ -5011,30 +5038,30 @@
         <v>-19</v>
       </c>
       <c r="G105" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H105" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I105" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J105">
         <v>4</v>
       </c>
       <c r="K105" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="L105">
         <v>6</v>
       </c>
       <c r="M105" t="s">
-        <v>29</v>
-      </c>
-      <c r="U105" t="s">
-        <v>33</v>
-      </c>
-      <c r="X105">
+        <v>33</v>
+      </c>
+      <c r="Z105" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB105">
         <v>11</v>
       </c>
     </row>
@@ -5046,7 +5073,7 @@
         <v>4</v>
       </c>
       <c r="C106" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D106">
         <v>3</v>
@@ -5058,13 +5085,13 @@
         <v>-23</v>
       </c>
       <c r="G106" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H106" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I106" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J106">
         <v>3</v>
@@ -5073,12 +5100,12 @@
         <v>6</v>
       </c>
       <c r="M106" t="s">
-        <v>51</v>
-      </c>
-      <c r="U106" t="s">
-        <v>33</v>
-      </c>
-      <c r="X106">
+        <v>55</v>
+      </c>
+      <c r="Z106" t="s">
+        <v>37</v>
+      </c>
+      <c r="AB106">
         <v>11</v>
       </c>
     </row>
@@ -5090,7 +5117,7 @@
         <v>4</v>
       </c>
       <c r="C107" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="D107">
         <v>4</v>
@@ -5102,15 +5129,15 @@
         <v>-26</v>
       </c>
       <c r="G107" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="H107" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="I107" t="s">
-        <v>68</v>
-      </c>
-      <c r="X107">
+        <v>72</v>
+      </c>
+      <c r="AB107">
         <v>11</v>
       </c>
     </row>
@@ -5122,7 +5149,7 @@
         <v>4</v>
       </c>
       <c r="C108" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D108">
         <v>1</v>
@@ -5134,13 +5161,13 @@
         <v>-49</v>
       </c>
       <c r="G108" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H108" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I108" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J108">
         <v>3</v>
@@ -5149,12 +5176,12 @@
         <v>5</v>
       </c>
       <c r="M108" t="s">
-        <v>37</v>
-      </c>
-      <c r="U108" t="s">
-        <v>36</v>
-      </c>
-      <c r="X108">
+        <v>41</v>
+      </c>
+      <c r="Z108" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB108">
         <v>12</v>
       </c>
     </row>
@@ -5166,7 +5193,7 @@
         <v>4</v>
       </c>
       <c r="C109" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D109">
         <v>2</v>
@@ -5178,13 +5205,13 @@
         <v>48</v>
       </c>
       <c r="G109" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="H109" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="I109" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="J109">
         <v>-16</v>
@@ -5192,7 +5219,7 @@
       <c r="L109">
         <v>6</v>
       </c>
-      <c r="X109">
+      <c r="AB109">
         <v>12</v>
       </c>
     </row>
@@ -5204,7 +5231,7 @@
         <v>4</v>
       </c>
       <c r="C110" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D110">
         <v>3</v>
@@ -5216,13 +5243,13 @@
         <v>-34</v>
       </c>
       <c r="G110" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H110" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I110" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J110">
         <v>3</v>
@@ -5231,12 +5258,12 @@
         <v>6</v>
       </c>
       <c r="M110" t="s">
-        <v>37</v>
-      </c>
-      <c r="U110" t="s">
-        <v>36</v>
-      </c>
-      <c r="X110">
+        <v>41</v>
+      </c>
+      <c r="Z110" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB110">
         <v>12</v>
       </c>
     </row>
